--- a/input/reg_fertility.xlsx
+++ b/input/reg_fertility.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
   <si>
     <t>Description:</t>
   </si>
@@ -104,13 +104,10 @@
     <t>demNChild0to2L1</t>
   </si>
   <si>
-    <t>eduHighestC4HighL1</t>
-  </si>
-  <si>
-    <t>eduHighestC4MediumL1</t>
-  </si>
-  <si>
-    <t>eduHighestC4LowL1</t>
+    <t>eduHighestC4Low</t>
+  </si>
+  <si>
+    <t>eduHighestC4High</t>
   </si>
   <si>
     <t>fertilityRate</t>
@@ -152,7 +149,7 @@
     <t>demRgnUKN</t>
   </si>
   <si>
-    <t>demYear</t>
+    <t>demYearTransformed</t>
   </si>
   <si>
     <t>demYear2020</t>
@@ -423,35 +420,35 @@
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4">
-        <v>0.16989956959399322</v>
+        <v>0.17138240451217646</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F4">
-        <v>1990.1848431645803</v>
+        <v>2022.062224502685</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5">
-        <v>82717</v>
+        <v>83159</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F5">
-        <v>-8376224.0149765806</v>
+        <v>-8357301.1977458587</v>
       </c>
     </row>
   </sheetData>
@@ -460,7 +457,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM38"/>
+  <dimension ref="A1:AL37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,127 +575,121 @@
       <c r="AL1" t="s">
         <v>50</v>
       </c>
-      <c r="AM1" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2">
-        <v>-0.25156199256879413</v>
+        <v>-0.53200332937532369</v>
       </c>
       <c r="C2">
-        <v>0.217223603926151</v>
+        <v>0.20543781327455188</v>
       </c>
       <c r="D2">
-        <v>-0.00033610629151956247</v>
+        <v>-9.1559453885857889e-005</v>
       </c>
       <c r="E2">
-        <v>4.9906404959750418e-006</v>
+        <v>1.603996211382189e-006</v>
       </c>
       <c r="F2">
-        <v>1.7400101916745022e-005</v>
+        <v>1.6131927792390168e-005</v>
       </c>
       <c r="G2">
-        <v>1.1122623558848158e-005</v>
+        <v>7.7183298111936107e-006</v>
       </c>
       <c r="H2">
-        <v>0.00054911823159658471</v>
+        <v>-6.2329879065248293e-005</v>
       </c>
       <c r="I2">
-        <v>0.0011526608879625783</v>
+        <v>0.0017474416667249268</v>
       </c>
       <c r="J2">
-        <v>-0.20778517557034798</v>
+        <v>-0.20477624704012615</v>
       </c>
       <c r="K2">
-        <v>-0.00021302426325534919</v>
+        <v>0.00015392599024654651</v>
       </c>
       <c r="L2">
-        <v>0.00043791964515932824</v>
+        <v>0.0012514904961599708</v>
       </c>
       <c r="M2">
-        <v>0.0012697973154632627</v>
+        <v>0.0020578423478267212</v>
       </c>
       <c r="N2">
-        <v>0.0017411285653893115</v>
+        <v>0.0024998240489301406</v>
       </c>
       <c r="O2">
-        <v>0.00035983244909435896</v>
+        <v>0.00035933179253314182</v>
       </c>
       <c r="P2">
-        <v>2.5682801096006984e-005</v>
+        <v>1.0113937214667327e-006</v>
       </c>
       <c r="Q2">
-        <v>0.0102315829392424</v>
+        <v>0.00049670434483377367</v>
       </c>
       <c r="R2">
-        <v>0.010199422762288841</v>
+        <v>0.00029322771365155502</v>
       </c>
       <c r="S2">
-        <v>0.010447853876029464</v>
+        <v>-0.00011888182959127831</v>
       </c>
       <c r="T2">
-        <v>-0.00014198997117942846</v>
+        <v>0.0010199109295059995</v>
       </c>
       <c r="U2">
-        <v>0.00052990570015204268</v>
+        <v>-0.00076867217283246945</v>
       </c>
       <c r="V2">
-        <v>-0.0011074628019153282</v>
+        <v>9.9843899083445348e-005</v>
       </c>
       <c r="W2">
-        <v>3.0193382082029617e-005</v>
+        <v>0.00033524910201420619</v>
       </c>
       <c r="X2">
-        <v>0.00025205799776496795</v>
+        <v>0.0002542012668357897</v>
       </c>
       <c r="Y2">
-        <v>0.00019167420371769502</v>
+        <v>0.0011485613489293509</v>
       </c>
       <c r="Z2">
-        <v>0.0011008121017136514</v>
+        <v>0.00074899313178353015</v>
       </c>
       <c r="AA2">
-        <v>0.00060029698893082455</v>
+        <v>-4.5955709517460277e-005</v>
       </c>
       <c r="AB2">
-        <v>-0.00013417223288986755</v>
+        <v>0.00024187105804528088</v>
       </c>
       <c r="AC2">
-        <v>0.00018028880580200262</v>
+        <v>0.00050489051232816039</v>
       </c>
       <c r="AD2">
-        <v>0.000291846511250104</v>
+        <v>-0.00015306899027832898</v>
       </c>
       <c r="AE2">
-        <v>-0.00033523854284169636</v>
+        <v>0.00027013316346486543</v>
       </c>
       <c r="AF2">
-        <v>8.6968597651502708e-005</v>
+        <v>-7.8786167833850537e-005</v>
       </c>
       <c r="AG2">
-        <v>-9.6348997729901173e-005</v>
+        <v>-0.00057531693783287492</v>
       </c>
       <c r="AH2">
-        <v>-0.00056375718196254726</v>
+        <v>-0.00029971967865791236</v>
       </c>
       <c r="AI2">
-        <v>-0.00018499049563647837</v>
+        <v>-5.652680391550393e-005</v>
       </c>
       <c r="AJ2">
-        <v>0.00012267086646320507</v>
+        <v>-0.00058324750785453952</v>
       </c>
       <c r="AK2">
-        <v>-0.00049944234047465293</v>
+        <v>0.0012766839756755237</v>
       </c>
       <c r="AL2">
-        <v>0.0012776473812648043</v>
-      </c>
-      <c r="AM2">
-        <v>0.0016507039351127129</v>
+        <v>0.0051150678178404213</v>
       </c>
     </row>
     <row r="3">
@@ -706,118 +697,115 @@
         <v>16</v>
       </c>
       <c r="B3">
-        <v>0.31741368352333743</v>
+        <v>0.32365262981949999</v>
       </c>
       <c r="C3">
-        <v>-0.00033610629151956247</v>
+        <v>-9.1559453885857889e-005</v>
       </c>
       <c r="D3">
-        <v>0.00031377794885359411</v>
+        <v>0.00029241702138337294</v>
       </c>
       <c r="E3">
-        <v>-4.6881357232857255e-006</v>
+        <v>-4.3926172333467645e-006</v>
       </c>
       <c r="F3">
-        <v>7.7305726255882536e-007</v>
+        <v>9.7499504372740299e-007</v>
       </c>
       <c r="G3">
-        <v>2.1190185180850463e-006</v>
+        <v>1.986137881633673e-006</v>
       </c>
       <c r="H3">
-        <v>1.7694444761764808e-005</v>
+        <v>2.6872953251219547e-005</v>
       </c>
       <c r="I3">
-        <v>8.1787371870659098e-005</v>
+        <v>6.9160856375666095e-005</v>
       </c>
       <c r="J3">
-        <v>0.00042213220797343316</v>
+        <v>0.00042444259764818889</v>
       </c>
       <c r="K3">
-        <v>-2.6387547350193493e-005</v>
+        <v>-1.8521320215619125e-005</v>
       </c>
       <c r="L3">
-        <v>-3.5713581684608346e-005</v>
+        <v>-4.094884112821977e-005</v>
       </c>
       <c r="M3">
-        <v>-4.6158705872185058e-005</v>
+        <v>-5.7913975177369559e-005</v>
       </c>
       <c r="N3">
-        <v>-9.9495523270052948e-005</v>
+        <v>-0.00011039133181760729</v>
       </c>
       <c r="O3">
-        <v>-3.7441546717449778e-005</v>
+        <v>-3.815443439177731e-005</v>
       </c>
       <c r="P3">
-        <v>-7.965909061907529e-005</v>
+        <v>-7.2795937571410493e-005</v>
       </c>
       <c r="Q3">
-        <v>-0.00032617901722270526</v>
+        <v>-3.7356494079785656e-005</v>
       </c>
       <c r="R3">
-        <v>-0.00031142883099790557</v>
+        <v>-9.6424489692912424e-006</v>
       </c>
       <c r="S3">
-        <v>-0.00035617484726398088</v>
+        <v>-9.5251835126580059e-006</v>
       </c>
       <c r="T3">
-        <v>-1.1337993431873809e-005</v>
+        <v>2.9250763117061058e-005</v>
       </c>
       <c r="U3">
-        <v>5.8479954139731451e-005</v>
+        <v>0.00010002735466648811</v>
       </c>
       <c r="V3">
-        <v>8.5971816482278564e-005</v>
+        <v>9.7696914191536038e-005</v>
       </c>
       <c r="W3">
-        <v>8.6724352162270094e-005</v>
+        <v>0.00015148120499576713</v>
       </c>
       <c r="X3">
-        <v>0.00013472511399825992</v>
+        <v>0.00015591486103541338</v>
       </c>
       <c r="Y3">
-        <v>0.0001784627749928795</v>
+        <v>0.00016376817462691743</v>
       </c>
       <c r="Z3">
-        <v>0.00015364260354093582</v>
+        <v>0.00023104011681060292</v>
       </c>
       <c r="AA3">
-        <v>0.00021545924894668302</v>
+        <v>0.00015391516887878798</v>
       </c>
       <c r="AB3">
-        <v>0.00014408899750075884</v>
+        <v>0.00016588269486408154</v>
       </c>
       <c r="AC3">
-        <v>0.00013941835798601202</v>
+        <v>0.00019472739121073547</v>
       </c>
       <c r="AD3">
-        <v>0.00018063089442444053</v>
+        <v>0.00014295161164169952</v>
       </c>
       <c r="AE3">
-        <v>0.00013462608533284148</v>
+        <v>0.00014514729913945191</v>
       </c>
       <c r="AF3">
-        <v>0.00013649797022068436</v>
+        <v>-7.56302292125289e-006</v>
       </c>
       <c r="AG3">
-        <v>-8.911273599796461e-006</v>
+        <v>-2.6537146479572483e-005</v>
       </c>
       <c r="AH3">
-        <v>-3.5243251367064223e-005</v>
+        <v>-5.5018858766613804e-005</v>
       </c>
       <c r="AI3">
-        <v>-8.2021987414312037e-005</v>
+        <v>5.1065744378084657e-006</v>
       </c>
       <c r="AJ3">
-        <v>-1.4458036443547144e-005</v>
+        <v>1.8028906569158079e-005</v>
       </c>
       <c r="AK3">
-        <v>-1.7499261623238078e-006</v>
+        <v>0.0002865514005017597</v>
       </c>
       <c r="AL3">
-        <v>0.00025715286964574438</v>
-      </c>
-      <c r="AM3">
-        <v>-0.0041141183581086017</v>
+        <v>-0.0041887917459276849</v>
       </c>
     </row>
     <row r="4">
@@ -825,118 +813,115 @@
         <v>17</v>
       </c>
       <c r="B4">
-        <v>-0.0056282812334667526</v>
+        <v>-0.0057059630422991456</v>
       </c>
       <c r="C4">
-        <v>4.9906404959750418e-006</v>
+        <v>1.603996211382189e-006</v>
       </c>
       <c r="D4">
-        <v>-4.6881357232857255e-006</v>
+        <v>-4.3926172333467645e-006</v>
       </c>
       <c r="E4">
-        <v>7.1240073950304205e-008</v>
+        <v>6.7170988231292586e-008</v>
       </c>
       <c r="F4">
-        <v>-4.0699606971812746e-009</v>
+        <v>-7.5019984687974812e-009</v>
       </c>
       <c r="G4">
-        <v>-3.1932555565528217e-008</v>
+        <v>-2.9713337336638846e-008</v>
       </c>
       <c r="H4">
-        <v>-3.8858078386922292e-007</v>
+        <v>-5.1024241868136276e-007</v>
       </c>
       <c r="I4">
-        <v>-8.493312472489142e-007</v>
+        <v>-6.72403152422202e-007</v>
       </c>
       <c r="J4">
-        <v>-6.236150432406643e-006</v>
+        <v>-6.2938531240626209e-006</v>
       </c>
       <c r="K4">
-        <v>4.7354662409825025e-007</v>
+        <v>3.0755203510189086e-007</v>
       </c>
       <c r="L4">
-        <v>5.8955347579079095e-007</v>
+        <v>6.2821410387102875e-007</v>
       </c>
       <c r="M4">
-        <v>5.095390749355945e-007</v>
+        <v>6.304796707600472e-007</v>
       </c>
       <c r="N4">
-        <v>1.304116032090738e-006</v>
+        <v>1.407533756233143e-006</v>
       </c>
       <c r="O4">
-        <v>3.4276583677961895e-007</v>
+        <v>3.5663546352233272e-007</v>
       </c>
       <c r="P4">
-        <v>1.4867623043410641e-006</v>
+        <v>1.3797988040752383e-006</v>
       </c>
       <c r="Q4">
-        <v>4.5468934853515149e-006</v>
+        <v>4.2759490528907412e-007</v>
       </c>
       <c r="R4">
-        <v>4.3315929785775425e-006</v>
+        <v>1.680336718549152e-007</v>
       </c>
       <c r="S4">
-        <v>4.8908514038084667e-006</v>
+        <v>1.6086958889698568e-007</v>
       </c>
       <c r="T4">
-        <v>1.8955816381488192e-007</v>
+        <v>-4.9421886907398326e-007</v>
       </c>
       <c r="U4">
-        <v>-9.0899788767463354e-007</v>
+        <v>-1.6460043078911126e-006</v>
       </c>
       <c r="V4">
-        <v>-1.4070648260265021e-006</v>
+        <v>-1.5113752313650239e-006</v>
       </c>
       <c r="W4">
-        <v>-1.336048458737508e-006</v>
+        <v>-2.2779225865855253e-006</v>
       </c>
       <c r="X4">
-        <v>-2.0077848392030662e-006</v>
+        <v>-2.4279442505935095e-006</v>
       </c>
       <c r="Y4">
-        <v>-2.7685251274408426e-006</v>
+        <v>-2.4522016072461152e-006</v>
       </c>
       <c r="Z4">
-        <v>-2.2859063054757216e-006</v>
+        <v>-3.6698382590131281e-006</v>
       </c>
       <c r="AA4">
-        <v>-3.4221294103590246e-006</v>
+        <v>-2.329387002131441e-006</v>
       </c>
       <c r="AB4">
-        <v>-2.1575606670473814e-006</v>
+        <v>-2.5452449907154385e-006</v>
       </c>
       <c r="AC4">
-        <v>-2.1330343543005354e-006</v>
+        <v>-2.9240620657251699e-006</v>
       </c>
       <c r="AD4">
-        <v>-2.7023727237877694e-006</v>
+        <v>-2.3713942299986163e-006</v>
       </c>
       <c r="AE4">
-        <v>-2.2157275030365852e-006</v>
+        <v>-2.2500566971706337e-006</v>
       </c>
       <c r="AF4">
-        <v>-2.1004172589964419e-006</v>
+        <v>1.2049351089588824e-007</v>
       </c>
       <c r="AG4">
-        <v>1.4246537473365746e-007</v>
+        <v>4.0155626947451227e-007</v>
       </c>
       <c r="AH4">
-        <v>5.406441439428816e-007</v>
+        <v>8.6914154417948184e-007</v>
       </c>
       <c r="AI4">
-        <v>1.2577644629238564e-006</v>
+        <v>-1.3338421361012596e-007</v>
       </c>
       <c r="AJ4">
-        <v>1.5938710802661287e-007</v>
+        <v>-5.2044630711463286e-007</v>
       </c>
       <c r="AK4">
-        <v>-2.1929725955146596e-007</v>
+        <v>-4.6057223438055665e-006</v>
       </c>
       <c r="AL4">
-        <v>-4.1672804853540345e-006</v>
-      </c>
-      <c r="AM4">
-        <v>5.9039867462360558e-005</v>
+        <v>6.0416784282312744e-005</v>
       </c>
     </row>
     <row r="5">
@@ -944,118 +929,115 @@
         <v>18</v>
       </c>
       <c r="B5">
-        <v>-0.013513486391714956</v>
+        <v>-0.013617803061419416</v>
       </c>
       <c r="C5">
-        <v>1.7400101916745022e-005</v>
+        <v>1.6131927792390168e-005</v>
       </c>
       <c r="D5">
-        <v>7.7305726255882536e-007</v>
+        <v>9.7499504372740299e-007</v>
       </c>
       <c r="E5">
-        <v>-4.0699606971812746e-009</v>
+        <v>-7.5019984687974812e-009</v>
       </c>
       <c r="F5">
-        <v>1.6485342128174609e-006</v>
+        <v>1.6308265485142816e-006</v>
       </c>
       <c r="G5">
-        <v>1.3819796107193959e-007</v>
+        <v>1.4519889198156783e-007</v>
       </c>
       <c r="H5">
-        <v>2.0012457897441729e-005</v>
+        <v>1.9685421041177796e-005</v>
       </c>
       <c r="I5">
-        <v>-1.8572744478928698e-005</v>
+        <v>-1.8309151149730716e-005</v>
       </c>
       <c r="J5">
-        <v>-2.0668660809436033e-005</v>
+        <v>-1.9337586012545653e-005</v>
       </c>
       <c r="K5">
-        <v>1.2085920403431954e-006</v>
+        <v>-3.2209628932112442e-007</v>
       </c>
       <c r="L5">
-        <v>-8.5017712915592889e-007</v>
+        <v>-1.6172073421182451e-006</v>
       </c>
       <c r="M5">
-        <v>-2.7068629333753952e-006</v>
+        <v>-3.3358111607067543e-006</v>
       </c>
       <c r="N5">
-        <v>-1.11399856024788e-005</v>
+        <v>-1.1716278585893853e-005</v>
       </c>
       <c r="O5">
-        <v>-3.0741921896188944e-006</v>
+        <v>-3.4036825970215676e-006</v>
       </c>
       <c r="P5">
-        <v>-7.9186546998027672e-007</v>
+        <v>-5.1477405488378426e-007</v>
       </c>
       <c r="Q5">
-        <v>2.4658105482023052e-006</v>
+        <v>6.2981877157942972e-007</v>
       </c>
       <c r="R5">
-        <v>-1.3218507986615129e-008</v>
+        <v>1.9492088234102386e-006</v>
       </c>
       <c r="S5">
-        <v>1.0355829237963498e-006</v>
+        <v>-7.6099522689724955e-007</v>
       </c>
       <c r="T5">
-        <v>-8.4881199299117394e-007</v>
+        <v>8.6450308998339418e-006</v>
       </c>
       <c r="U5">
-        <v>8.0994428268973417e-006</v>
+        <v>2.3840960654158269e-006</v>
       </c>
       <c r="V5">
-        <v>2.2097895872994584e-006</v>
+        <v>4.8115884531056557e-006</v>
       </c>
       <c r="W5">
-        <v>4.4210011579929542e-006</v>
+        <v>3.6774430108213565e-006</v>
       </c>
       <c r="X5">
-        <v>3.6529729111338584e-006</v>
+        <v>2.4271270391688767e-006</v>
       </c>
       <c r="Y5">
-        <v>1.3547097494412623e-006</v>
+        <v>3.4114284080595614e-006</v>
       </c>
       <c r="Z5">
-        <v>3.2285176272676075e-006</v>
+        <v>1.0082272882256399e-005</v>
       </c>
       <c r="AA5">
-        <v>9.8500381987626435e-006</v>
+        <v>2.7490599463574994e-007</v>
       </c>
       <c r="AB5">
-        <v>5.0043655215772424e-007</v>
+        <v>3.469416830102173e-006</v>
       </c>
       <c r="AC5">
-        <v>4.2949284276583988e-006</v>
+        <v>4.6442823837224826e-006</v>
       </c>
       <c r="AD5">
-        <v>4.4970639056239545e-006</v>
+        <v>-1.8014601718396664e-006</v>
       </c>
       <c r="AE5">
-        <v>-1.8421644278118342e-006</v>
+        <v>1.4908629322377657e-006</v>
       </c>
       <c r="AF5">
-        <v>1.3523906111505447e-006</v>
+        <v>-5.7593407553714627e-007</v>
       </c>
       <c r="AG5">
-        <v>-7.0758071077323385e-007</v>
+        <v>-3.7426835891981924e-006</v>
       </c>
       <c r="AH5">
-        <v>-3.3773874322428818e-006</v>
+        <v>1.0272851738511629e-006</v>
       </c>
       <c r="AI5">
-        <v>1.2229827263314052e-006</v>
+        <v>1.5691615755791336e-006</v>
       </c>
       <c r="AJ5">
-        <v>1.4643168722367507e-006</v>
+        <v>1.5085316360954403e-006</v>
       </c>
       <c r="AK5">
-        <v>1.3734581828507825e-006</v>
+        <v>1.7675754068946156e-005</v>
       </c>
       <c r="AL5">
-        <v>1.7868796407769091e-005</v>
-      </c>
-      <c r="AM5">
-        <v>-4.974261260235033e-005</v>
+        <v>-5.8295662480047636e-005</v>
       </c>
     </row>
     <row r="6">
@@ -1063,118 +1045,115 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>0.0067909196844282661</v>
+        <v>0.007005085008673897</v>
       </c>
       <c r="C6">
-        <v>1.1122623558848158e-005</v>
+        <v>7.7183298111936107e-006</v>
       </c>
       <c r="D6">
-        <v>2.1190185180850463e-006</v>
+        <v>1.986137881633673e-006</v>
       </c>
       <c r="E6">
-        <v>-3.1932555565528217e-008</v>
+        <v>-2.9713337336638846e-008</v>
       </c>
       <c r="F6">
-        <v>1.3819796107193959e-007</v>
+        <v>1.4519889198156783e-007</v>
       </c>
       <c r="G6">
-        <v>1.6151779151848173e-006</v>
+        <v>1.6146577651911893e-006</v>
       </c>
       <c r="H6">
-        <v>1.1440320032956803e-005</v>
+        <v>1.1506165721486187e-005</v>
       </c>
       <c r="I6">
-        <v>-2.0896861369417221e-005</v>
+        <v>-2.082490239091591e-005</v>
       </c>
       <c r="J6">
-        <v>-6.6014742209641466e-006</v>
+        <v>-5.6175138289102375e-006</v>
       </c>
       <c r="K6">
-        <v>-3.3096013867918684e-006</v>
+        <v>-3.1518507109137321e-006</v>
       </c>
       <c r="L6">
-        <v>-8.619178043703148e-006</v>
+        <v>-9.2327084277554338e-006</v>
       </c>
       <c r="M6">
-        <v>-1.6161616641176987e-005</v>
+        <v>-1.6812470195910457e-005</v>
       </c>
       <c r="N6">
-        <v>-1.3308363103015295e-005</v>
+        <v>-1.3704425154398655e-005</v>
       </c>
       <c r="O6">
-        <v>-2.6634375283017533e-006</v>
+        <v>-2.329262762653658e-006</v>
       </c>
       <c r="P6">
-        <v>4.5349758374722388e-008</v>
+        <v>-1.2336917663742062e-007</v>
       </c>
       <c r="Q6">
-        <v>-6.0258932343264948e-007</v>
+        <v>1.0685483222414431e-006</v>
       </c>
       <c r="R6">
-        <v>1.8518830503332305e-006</v>
+        <v>-2.4121673474032823e-006</v>
       </c>
       <c r="S6">
-        <v>3.3710789857197037e-006</v>
+        <v>1.2243568445699281e-006</v>
       </c>
       <c r="T6">
-        <v>1.2885670211706606e-006</v>
+        <v>4.2043462389814579e-006</v>
       </c>
       <c r="U6">
-        <v>4.60083982283042e-006</v>
+        <v>-4.2902152116876318e-006</v>
       </c>
       <c r="V6">
-        <v>-4.155185354995559e-006</v>
+        <v>-4.7004202082222364e-006</v>
       </c>
       <c r="W6">
-        <v>-4.5305505278542616e-006</v>
+        <v>-3.0597444992348512e-006</v>
       </c>
       <c r="X6">
-        <v>-2.9445526438273674e-006</v>
+        <v>-2.4433196165733625e-006</v>
       </c>
       <c r="Y6">
-        <v>-2.7474816995351886e-006</v>
+        <v>-2.38893241984942e-006</v>
       </c>
       <c r="Z6">
-        <v>-2.2486698792265617e-006</v>
+        <v>-1.3634444692037891e-005</v>
       </c>
       <c r="AA6">
-        <v>-1.3162899400323308e-005</v>
+        <v>-3.7931236235367004e-006</v>
       </c>
       <c r="AB6">
-        <v>-3.5954298320892207e-006</v>
+        <v>-3.6845379686415348e-006</v>
       </c>
       <c r="AC6">
-        <v>-4.4167458056904373e-006</v>
+        <v>-7.5229560360237169e-006</v>
       </c>
       <c r="AD6">
-        <v>-7.318469928957008e-006</v>
+        <v>-5.2673926168255624e-006</v>
       </c>
       <c r="AE6">
-        <v>-5.1417184329700977e-006</v>
+        <v>-3.6880853750586828e-006</v>
       </c>
       <c r="AF6">
-        <v>-3.5026009717748754e-006</v>
+        <v>1.4605478834024842e-006</v>
       </c>
       <c r="AG6">
-        <v>1.5367247133585213e-006</v>
+        <v>6.2259686470278653e-006</v>
       </c>
       <c r="AH6">
-        <v>6.5949326141458778e-006</v>
+        <v>7.7950723154255991e-006</v>
       </c>
       <c r="AI6">
-        <v>7.8741596823225976e-006</v>
+        <v>-6.773704474306016e-007</v>
       </c>
       <c r="AJ6">
-        <v>-5.1269022852124618e-007</v>
+        <v>1.1410059634496249e-006</v>
       </c>
       <c r="AK6">
-        <v>1.3234515750249751e-006</v>
+        <v>-3.0767736225818495e-005</v>
       </c>
       <c r="AL6">
-        <v>-3.1001578646098902e-005</v>
-      </c>
-      <c r="AM6">
-        <v>-0.00020024178315272156</v>
+        <v>-0.00019155574543252437</v>
       </c>
     </row>
     <row r="7">
@@ -1182,118 +1161,115 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-0.72571036953199419</v>
+        <v>-0.72395165710909692</v>
       </c>
       <c r="C7">
-        <v>0.00054911823159658471</v>
+        <v>-6.2329879065248293e-005</v>
       </c>
       <c r="D7">
-        <v>1.7694444761764808e-005</v>
+        <v>2.6872953251219547e-005</v>
       </c>
       <c r="E7">
-        <v>-3.8858078386922292e-007</v>
+        <v>-5.1024241868136276e-007</v>
       </c>
       <c r="F7">
-        <v>2.0012457897441729e-005</v>
+        <v>1.9685421041177796e-005</v>
       </c>
       <c r="G7">
-        <v>1.1440320032956803e-005</v>
+        <v>1.1506165721486187e-005</v>
       </c>
       <c r="H7">
-        <v>0.0067424412571119837</v>
+        <v>0.0068494050061718706</v>
       </c>
       <c r="I7">
-        <v>-0.006030519621455197</v>
+        <v>-0.0061399448261742796</v>
       </c>
       <c r="J7">
-        <v>-0.00051113327455829178</v>
+        <v>-0.0003669673328286274</v>
       </c>
       <c r="K7">
-        <v>-6.2755800096247168e-005</v>
+        <v>-1.5306530931814822e-005</v>
       </c>
       <c r="L7">
-        <v>7.6211589680132732e-006</v>
+        <v>9.704464094665201e-005</v>
       </c>
       <c r="M7">
-        <v>-7.9875983879528932e-006</v>
+        <v>9.5613153694506023e-005</v>
       </c>
       <c r="N7">
-        <v>-0.00033557454665997103</v>
+        <v>-0.00024341367877990234</v>
       </c>
       <c r="O7">
-        <v>0.00011886030616974281</v>
+        <v>0.0001076567738074946</v>
       </c>
       <c r="P7">
-        <v>-0.00016258252428948114</v>
+        <v>-0.0001422553832980845</v>
       </c>
       <c r="Q7">
-        <v>0.0010955470431101288</v>
+        <v>0.00013685166363699882</v>
       </c>
       <c r="R7">
-        <v>0.00057527362762469208</v>
+        <v>0.0005137867258616617</v>
       </c>
       <c r="S7">
-        <v>0.00067333774121396779</v>
+        <v>4.0060671806974538e-005</v>
       </c>
       <c r="T7">
-        <v>3.2961652580161911e-005</v>
+        <v>0.00010029412965184243</v>
       </c>
       <c r="U7">
-        <v>5.5767346755378381e-005</v>
+        <v>-0.00010528942491672935</v>
       </c>
       <c r="V7">
-        <v>-0.00016654237020553283</v>
+        <v>6.1315621847286546e-005</v>
       </c>
       <c r="W7">
-        <v>3.5748213693306916e-005</v>
+        <v>5.3322173083817802e-005</v>
       </c>
       <c r="X7">
-        <v>3.9597475021291122e-005</v>
+        <v>1.0231736943888079e-006</v>
       </c>
       <c r="Y7">
-        <v>4.3474083207095515e-005</v>
+        <v>-0.00010488322641709349</v>
       </c>
       <c r="Z7">
-        <v>-0.0001235650547236294</v>
+        <v>0.00051918324552543635</v>
       </c>
       <c r="AA7">
-        <v>0.0005020151131680463</v>
+        <v>-0.0003721287412152701</v>
       </c>
       <c r="AB7">
-        <v>-0.00037101907844401408</v>
+        <v>-1.7790452162926219e-006</v>
       </c>
       <c r="AC7">
-        <v>1.7877426506447027e-005</v>
+        <v>7.732346975928806e-005</v>
       </c>
       <c r="AD7">
-        <v>5.4914822257967914e-005</v>
+        <v>-0.00075539575584244122</v>
       </c>
       <c r="AE7">
-        <v>-0.00076517547670724366</v>
+        <v>-0.00013285985941549426</v>
       </c>
       <c r="AF7">
-        <v>-0.00014617153448102309</v>
+        <v>2.6982426093706637e-005</v>
       </c>
       <c r="AG7">
-        <v>2.0891420905773262e-005</v>
+        <v>-1.6929237222918203e-005</v>
       </c>
       <c r="AH7">
-        <v>-3.3210052751427618e-005</v>
+        <v>0.000149165522473258</v>
       </c>
       <c r="AI7">
-        <v>0.00011757775743287304</v>
+        <v>-7.896401514970858e-005</v>
       </c>
       <c r="AJ7">
-        <v>-7.841393178064694e-005</v>
+        <v>-0.00031903731942996576</v>
       </c>
       <c r="AK7">
-        <v>-0.00032331174718122424</v>
+        <v>0.00038975016598094461</v>
       </c>
       <c r="AL7">
-        <v>0.00035913374482540511</v>
-      </c>
-      <c r="AM7">
-        <v>-0.0048025385726116337</v>
+        <v>-0.0049979091070046656</v>
       </c>
     </row>
     <row r="8">
@@ -1301,118 +1277,115 @@
         <v>21</v>
       </c>
       <c r="B8">
-        <v>0.13126392132236714</v>
+        <v>0.11626848781660369</v>
       </c>
       <c r="C8">
-        <v>0.0011526608879625783</v>
+        <v>0.0017474416667249268</v>
       </c>
       <c r="D8">
-        <v>8.1787371870659098e-005</v>
+        <v>6.9160856375666095e-005</v>
       </c>
       <c r="E8">
-        <v>-8.493312472489142e-007</v>
+        <v>-6.72403152422202e-007</v>
       </c>
       <c r="F8">
-        <v>-1.8572744478928698e-005</v>
+        <v>-1.8309151149730716e-005</v>
       </c>
       <c r="G8">
-        <v>-2.0896861369417221e-005</v>
+        <v>-2.082490239091591e-005</v>
       </c>
       <c r="H8">
-        <v>-0.006030519621455197</v>
+        <v>-0.0061399448261742796</v>
       </c>
       <c r="I8">
-        <v>0.0069698107728511198</v>
+        <v>0.0070865603274469901</v>
       </c>
       <c r="J8">
-        <v>-0.0012619237121219689</v>
+        <v>-0.0013939435168956976</v>
       </c>
       <c r="K8">
-        <v>0.00018804496202482089</v>
+        <v>0.00015775543185081334</v>
       </c>
       <c r="L8">
-        <v>0.00057066191956267284</v>
+        <v>0.00053083147761895291</v>
       </c>
       <c r="M8">
-        <v>0.00099978288572434354</v>
+        <v>0.00094749738752378417</v>
       </c>
       <c r="N8">
-        <v>0.001207096741080383</v>
+        <v>0.0011450639612123194</v>
       </c>
       <c r="O8">
-        <v>0.00011658934943760391</v>
+        <v>0.00011569640792940953</v>
       </c>
       <c r="P8">
-        <v>0.00019851202789831137</v>
+        <v>0.00020508342396619042</v>
       </c>
       <c r="Q8">
-        <v>-0.00088764034978694147</v>
+        <v>0.0001265646273506865</v>
       </c>
       <c r="R8">
-        <v>-0.00055032247543040295</v>
+        <v>-0.00032397927403205362</v>
       </c>
       <c r="S8">
-        <v>-0.00043129017231416096</v>
+        <v>-5.3409189011997924e-005</v>
       </c>
       <c r="T8">
-        <v>-5.1320804953352336e-005</v>
+        <v>-2.8388705261737994e-006</v>
       </c>
       <c r="U8">
-        <v>3.6497749604622379e-005</v>
+        <v>9.625053137307306e-005</v>
       </c>
       <c r="V8">
-        <v>0.00016064438442527204</v>
+        <v>2.7722529029481345e-005</v>
       </c>
       <c r="W8">
-        <v>4.7447159831332788e-005</v>
+        <v>9.3460319157949705e-005</v>
       </c>
       <c r="X8">
-        <v>0.00011338948250712218</v>
+        <v>2.5625850678215843e-005</v>
       </c>
       <c r="Y8">
-        <v>5.3550561024909879e-005</v>
+        <v>0.00012023779858716811</v>
       </c>
       <c r="Z8">
-        <v>0.00015575580233343205</v>
+        <v>0.00020126442066449894</v>
       </c>
       <c r="AA8">
-        <v>0.00019989892680981119</v>
+        <v>0.00043812760120408225</v>
       </c>
       <c r="AB8">
-        <v>0.00046517043840930159</v>
+        <v>0.00015704120578152552</v>
       </c>
       <c r="AC8">
-        <v>0.00019083186297889438</v>
+        <v>0.00021483790110557379</v>
       </c>
       <c r="AD8">
-        <v>0.00024136483846119022</v>
+        <v>0.00071916467808292889</v>
       </c>
       <c r="AE8">
-        <v>0.00074796759064719802</v>
+        <v>7.7924201770455861e-005</v>
       </c>
       <c r="AF8">
-        <v>0.00010320281194527723</v>
+        <v>-2.4816777708662356e-005</v>
       </c>
       <c r="AG8">
-        <v>-2.4316231834377449e-005</v>
+        <v>-0.00032987204953516995</v>
       </c>
       <c r="AH8">
-        <v>-0.00031736160748354215</v>
+        <v>-0.00044900559712765325</v>
       </c>
       <c r="AI8">
-        <v>-0.00041173802828243654</v>
+        <v>7.0945308717769223e-005</v>
       </c>
       <c r="AJ8">
-        <v>6.4445621554079686e-005</v>
+        <v>-0.00024893662899198551</v>
       </c>
       <c r="AK8">
-        <v>-0.00023658805361457787</v>
+        <v>0.0017561149839221031</v>
       </c>
       <c r="AL8">
-        <v>0.001702080966160811</v>
-      </c>
-      <c r="AM8">
-        <v>0.0028352063710509329</v>
+        <v>0.0026945097980674293</v>
       </c>
     </row>
     <row r="9">
@@ -1420,118 +1393,115 @@
         <v>22</v>
       </c>
       <c r="B9">
-        <v>-0.39495206596026028</v>
+        <v>-0.33554018831731613</v>
       </c>
       <c r="C9">
-        <v>-0.20778517557034798</v>
+        <v>-0.20477624704012615</v>
       </c>
       <c r="D9">
-        <v>0.00042213220797343316</v>
+        <v>0.00042444259764818889</v>
       </c>
       <c r="E9">
-        <v>-6.236150432406643e-006</v>
+        <v>-6.2938531240626209e-006</v>
       </c>
       <c r="F9">
-        <v>-2.0668660809436033e-005</v>
+        <v>-1.9337586012545653e-005</v>
       </c>
       <c r="G9">
-        <v>-6.6014742209641466e-006</v>
+        <v>-5.6175138289102375e-006</v>
       </c>
       <c r="H9">
-        <v>-0.00051113327455829178</v>
+        <v>-0.0003669673328286274</v>
       </c>
       <c r="I9">
-        <v>-0.0012619237121219689</v>
+        <v>-0.0013939435168956976</v>
       </c>
       <c r="J9">
-        <v>0.23329303742729715</v>
+        <v>0.22874990768027903</v>
       </c>
       <c r="K9">
-        <v>0.00023354303669130834</v>
+        <v>0.00014642178210157441</v>
       </c>
       <c r="L9">
-        <v>-0.00045050659651483187</v>
+        <v>-0.00054472586480478727</v>
       </c>
       <c r="M9">
-        <v>-0.0012698607317472692</v>
+        <v>-0.0014271512839656103</v>
       </c>
       <c r="N9">
-        <v>-0.0017009830834254676</v>
+        <v>-0.0018537725669807814</v>
       </c>
       <c r="O9">
-        <v>-0.00037916909427463026</v>
+        <v>-0.00037441032905224047</v>
       </c>
       <c r="P9">
-        <v>-5.64259620386002e-005</v>
+        <v>-9.5999728761143486e-005</v>
       </c>
       <c r="Q9">
-        <v>-0.0010291078527164205</v>
+        <v>-0.00038093747183944705</v>
       </c>
       <c r="R9">
-        <v>-0.00090875650235321722</v>
+        <v>-0.0001095571767722503</v>
       </c>
       <c r="S9">
-        <v>-0.0012163947045443311</v>
+        <v>0.00012710126904816034</v>
       </c>
       <c r="T9">
-        <v>0.00012995542925907226</v>
+        <v>-0.00055007105061917732</v>
       </c>
       <c r="U9">
-        <v>-0.00050011709093738914</v>
+        <v>0.00068504499296967892</v>
       </c>
       <c r="V9">
-        <v>0.00070834421062997209</v>
+        <v>-6.766603457855825e-005</v>
       </c>
       <c r="W9">
-        <v>-7.0992073392485612e-005</v>
+        <v>0.0003800076857157507</v>
       </c>
       <c r="X9">
-        <v>0.00040858019270463434</v>
+        <v>-7.4020544988011533e-005</v>
       </c>
       <c r="Y9">
-        <v>-0.00016681250310410654</v>
+        <v>-0.00099234758414382942</v>
       </c>
       <c r="Z9">
-        <v>-0.0010819187583191196</v>
+        <v>-0.00071630488343343748</v>
       </c>
       <c r="AA9">
-        <v>-0.00073081431253175155</v>
+        <v>0.00014257303752827043</v>
       </c>
       <c r="AB9">
-        <v>0.00012973320962810292</v>
+        <v>-7.3443682259383505e-005</v>
       </c>
       <c r="AC9">
-        <v>-0.00013206245752876963</v>
+        <v>-0.00029166135258044165</v>
       </c>
       <c r="AD9">
-        <v>-0.00030052754175893684</v>
+        <v>0.0001929046550001304</v>
       </c>
       <c r="AE9">
-        <v>0.000197154631043704</v>
+        <v>-0.00011321760410935953</v>
       </c>
       <c r="AF9">
-        <v>-0.00010957095615421876</v>
+        <v>8.0922425879660377e-005</v>
       </c>
       <c r="AG9">
-        <v>8.1711130071494554e-005</v>
+        <v>0.00061298317654607604</v>
       </c>
       <c r="AH9">
-        <v>0.00062194645657981688</v>
+        <v>0.00019641808547011733</v>
       </c>
       <c r="AI9">
-        <v>0.0002014568059194909</v>
+        <v>-0.00026688485360133187</v>
       </c>
       <c r="AJ9">
-        <v>-0.00028472211757559477</v>
+        <v>0.00050394462782265409</v>
       </c>
       <c r="AK9">
-        <v>0.00053385650180145182</v>
+        <v>-0.0017520966706413526</v>
       </c>
       <c r="AL9">
-        <v>-0.0017438329997150647</v>
-      </c>
-      <c r="AM9">
-        <v>-0.011405369249832899</v>
+        <v>-0.012132987121470247</v>
       </c>
     </row>
     <row r="10">
@@ -1539,118 +1509,115 @@
         <v>23</v>
       </c>
       <c r="B10">
-        <v>-0.044322700626562406</v>
+        <v>-0.015456526885211076</v>
       </c>
       <c r="C10">
-        <v>-0.00021302426325534919</v>
+        <v>0.00015392599024654651</v>
       </c>
       <c r="D10">
-        <v>-2.6387547350193493e-005</v>
+        <v>-1.8521320215619125e-005</v>
       </c>
       <c r="E10">
-        <v>4.7354662409825025e-007</v>
+        <v>3.0755203510189086e-007</v>
       </c>
       <c r="F10">
-        <v>1.2085920403431954e-006</v>
+        <v>-3.2209628932112442e-007</v>
       </c>
       <c r="G10">
-        <v>-3.3096013867918684e-006</v>
+        <v>-3.1518507109137321e-006</v>
       </c>
       <c r="H10">
-        <v>-6.2755800096247168e-005</v>
+        <v>-1.5306530931814822e-005</v>
       </c>
       <c r="I10">
-        <v>0.00018804496202482089</v>
+        <v>0.00015775543185081334</v>
       </c>
       <c r="J10">
-        <v>0.00023354303669130834</v>
+        <v>0.00014642178210157441</v>
       </c>
       <c r="K10">
-        <v>0.0027075246704723311</v>
+        <v>0.0025847514780244826</v>
       </c>
       <c r="L10">
-        <v>0.0016273254670777855</v>
+        <v>0.0015139789819154589</v>
       </c>
       <c r="M10">
-        <v>0.0016766608423862007</v>
+        <v>0.0015656336700359632</v>
       </c>
       <c r="N10">
-        <v>0.001591587028870513</v>
+        <v>0.0014685333092138062</v>
       </c>
       <c r="O10">
-        <v>-0.00021610883532231732</v>
+        <v>-0.00021847746608245466</v>
       </c>
       <c r="P10">
-        <v>7.3163995802980565e-005</v>
+        <v>5.2407980440579609e-005</v>
       </c>
       <c r="Q10">
-        <v>-0.00042066767075136504</v>
+        <v>-2.1166851585592062e-006</v>
       </c>
       <c r="R10">
-        <v>-0.0004151299276894555</v>
+        <v>1.4675730200645789e-005</v>
       </c>
       <c r="S10">
-        <v>-0.00035363258624349607</v>
+        <v>-2.7615825078436737e-005</v>
       </c>
       <c r="T10">
-        <v>-2.1727292845972831e-005</v>
+        <v>0.00032516273591916387</v>
       </c>
       <c r="U10">
-        <v>0.00035005040671948478</v>
+        <v>0.00016448988830125791</v>
       </c>
       <c r="V10">
-        <v>0.00015007271903986856</v>
+        <v>0.00012812622383470042</v>
       </c>
       <c r="W10">
-        <v>0.00010877662826730133</v>
+        <v>5.1012743587666192e-005</v>
       </c>
       <c r="X10">
-        <v>5.3210594658557625e-005</v>
+        <v>7.5102046503341881e-005</v>
       </c>
       <c r="Y10">
-        <v>-7.544271015863131e-005</v>
+        <v>4.1714865828999196e-005</v>
       </c>
       <c r="Z10">
-        <v>3.7186797125790836e-005</v>
+        <v>0.0002411140451282739</v>
       </c>
       <c r="AA10">
-        <v>0.00020931618340061921</v>
+        <v>0.00010903687405521687</v>
       </c>
       <c r="AB10">
-        <v>0.00010088482246977656</v>
+        <v>6.9897023413304144e-005</v>
       </c>
       <c r="AC10">
-        <v>9.9822365165813014e-005</v>
+        <v>4.8351911503920545e-005</v>
       </c>
       <c r="AD10">
-        <v>4.5888264616702362e-005</v>
+        <v>-9.021305577256968e-005</v>
       </c>
       <c r="AE10">
-        <v>-7.520566641779845e-005</v>
+        <v>0.00023199438151691497</v>
       </c>
       <c r="AF10">
-        <v>0.00023394760552095681</v>
+        <v>-3.649893703404745e-005</v>
       </c>
       <c r="AG10">
-        <v>-3.2849143929438887e-005</v>
+        <v>-1.8475101305817144e-005</v>
       </c>
       <c r="AH10">
-        <v>6.3573291048267446e-006</v>
+        <v>6.1964233863514889e-005</v>
       </c>
       <c r="AI10">
-        <v>8.8196267273086171e-005</v>
+        <v>-0.00017988181928324374</v>
       </c>
       <c r="AJ10">
-        <v>-0.0001838264104221798</v>
+        <v>0.00018855087991724335</v>
       </c>
       <c r="AK10">
-        <v>0.00019831270147734574</v>
+        <v>0.00043575863269854596</v>
       </c>
       <c r="AL10">
-        <v>0.00041130176588057531</v>
-      </c>
-      <c r="AM10">
-        <v>0.0010883399077574315</v>
+        <v>0.001181021398127916</v>
       </c>
     </row>
     <row r="11">
@@ -1658,118 +1625,115 @@
         <v>24</v>
       </c>
       <c r="B11">
-        <v>-0.1393718525626931</v>
+        <v>-0.11603842157620138</v>
       </c>
       <c r="C11">
-        <v>0.00043791964515932824</v>
+        <v>0.0012514904961599708</v>
       </c>
       <c r="D11">
-        <v>-3.5713581684608346e-005</v>
+        <v>-4.094884112821977e-005</v>
       </c>
       <c r="E11">
-        <v>5.8955347579079095e-007</v>
+        <v>6.2821410387102875e-007</v>
       </c>
       <c r="F11">
-        <v>-8.5017712915592889e-007</v>
+        <v>-1.6172073421182451e-006</v>
       </c>
       <c r="G11">
-        <v>-8.619178043703148e-006</v>
+        <v>-9.2327084277554338e-006</v>
       </c>
       <c r="H11">
-        <v>7.6211589680132732e-006</v>
+        <v>9.704464094665201e-005</v>
       </c>
       <c r="I11">
-        <v>0.00057066191956267284</v>
+        <v>0.00053083147761895291</v>
       </c>
       <c r="J11">
-        <v>-0.00045050659651483187</v>
+        <v>-0.00054472586480478727</v>
       </c>
       <c r="K11">
-        <v>0.0016273254670777855</v>
+        <v>0.0015139789819154589</v>
       </c>
       <c r="L11">
-        <v>0.0027346068236314175</v>
+        <v>0.0025793824043396718</v>
       </c>
       <c r="M11">
-        <v>0.0022100279211547864</v>
+        <v>0.002066127339565591</v>
       </c>
       <c r="N11">
-        <v>0.0021656610802906354</v>
+        <v>0.0019928657707270719</v>
       </c>
       <c r="O11">
-        <v>-8.1126396499593245e-005</v>
+        <v>-6.3787894216452802e-005</v>
       </c>
       <c r="P11">
-        <v>3.3133869317861561e-005</v>
+        <v>1.6273946601051163e-006</v>
       </c>
       <c r="Q11">
-        <v>-0.00091763003509725887</v>
+        <v>0.00018597997617051835</v>
       </c>
       <c r="R11">
-        <v>-0.00092051597997631516</v>
+        <v>6.5609535066008537e-005</v>
       </c>
       <c r="S11">
-        <v>-0.00068552240126297948</v>
+        <v>-5.2002625690307014e-005</v>
       </c>
       <c r="T11">
-        <v>-4.0108910420128815e-005</v>
+        <v>0.00056753835923690555</v>
       </c>
       <c r="U11">
-        <v>0.00063252799218317061</v>
+        <v>3.2929314734775178e-005</v>
       </c>
       <c r="V11">
-        <v>1.148014912290795e-005</v>
+        <v>9.2500495107306741e-005</v>
       </c>
       <c r="W11">
-        <v>8.9784346590368879e-005</v>
+        <v>3.6926477130641574e-005</v>
       </c>
       <c r="X11">
-        <v>3.5242119872064503e-005</v>
+        <v>3.508278580626118e-006</v>
       </c>
       <c r="Y11">
-        <v>-0.00012409300974720907</v>
+        <v>-2.9575608927579205e-005</v>
       </c>
       <c r="Z11">
-        <v>-3.1997367791196287e-005</v>
+        <v>0.00035881530777383958</v>
       </c>
       <c r="AA11">
-        <v>0.00031009742604268514</v>
+        <v>4.3008552664827021e-005</v>
       </c>
       <c r="AB11">
-        <v>4.6426937158933863e-005</v>
+        <v>4.7475844356725816e-005</v>
       </c>
       <c r="AC11">
-        <v>4.5260501006750799e-005</v>
+        <v>0.00025612766105230814</v>
       </c>
       <c r="AD11">
-        <v>0.00025299492889766331</v>
+        <v>-5.8992872018659383e-005</v>
       </c>
       <c r="AE11">
-        <v>-3.3782554708199455e-005</v>
+        <v>0.00013222417462586847</v>
       </c>
       <c r="AF11">
-        <v>0.00014582347394210843</v>
+        <v>-5.0776866518007389e-005</v>
       </c>
       <c r="AG11">
-        <v>-4.2051431883492871e-005</v>
+        <v>-0.00013007171642184659</v>
       </c>
       <c r="AH11">
-        <v>-8.835946198237671e-005</v>
+        <v>-9.7687323686359239e-005</v>
       </c>
       <c r="AI11">
-        <v>-3.0498484198491637e-005</v>
+        <v>-0.00017376644155001606</v>
       </c>
       <c r="AJ11">
-        <v>-0.00018331029926357313</v>
+        <v>5.2640332745617529e-005</v>
       </c>
       <c r="AK11">
-        <v>7.6012699823187061e-005</v>
+        <v>0.001052518297543212</v>
       </c>
       <c r="AL11">
-        <v>0.00095399970196039571</v>
-      </c>
-      <c r="AM11">
-        <v>0.0026324239523177273</v>
+        <v>0.0028666716242164037</v>
       </c>
     </row>
     <row r="12">
@@ -1777,118 +1741,115 @@
         <v>25</v>
       </c>
       <c r="B12">
-        <v>-0.13770024016005541</v>
+        <v>-0.10383679472691418</v>
       </c>
       <c r="C12">
-        <v>0.0012697973154632627</v>
+        <v>0.0020578423478267212</v>
       </c>
       <c r="D12">
-        <v>-4.6158705872185058e-005</v>
+        <v>-5.7913975177369559e-005</v>
       </c>
       <c r="E12">
-        <v>5.095390749355945e-007</v>
+        <v>6.304796707600472e-007</v>
       </c>
       <c r="F12">
-        <v>-2.7068629333753952e-006</v>
+        <v>-3.3358111607067543e-006</v>
       </c>
       <c r="G12">
-        <v>-1.6161616641176987e-005</v>
+        <v>-1.6812470195910457e-005</v>
       </c>
       <c r="H12">
-        <v>-7.9875983879528932e-006</v>
+        <v>9.5613153694506023e-005</v>
       </c>
       <c r="I12">
-        <v>0.00099978288572434354</v>
+        <v>0.00094749738752378417</v>
       </c>
       <c r="J12">
-        <v>-0.0012698607317472692</v>
+        <v>-0.0014271512839656103</v>
       </c>
       <c r="K12">
-        <v>0.0016766608423862007</v>
+        <v>0.0015656336700359632</v>
       </c>
       <c r="L12">
-        <v>0.0022100279211547864</v>
+        <v>0.002066127339565591</v>
       </c>
       <c r="M12">
-        <v>0.003336529043805618</v>
+        <v>0.0032149706667908857</v>
       </c>
       <c r="N12">
-        <v>0.0026035985994619991</v>
+        <v>0.00243646048019831</v>
       </c>
       <c r="O12">
-        <v>1.2288848817269593e-005</v>
+        <v>3.0343330767699259e-005</v>
       </c>
       <c r="P12">
-        <v>2.1602949602143793e-005</v>
+        <v>-9.0521128922805465e-006</v>
       </c>
       <c r="Q12">
-        <v>-0.00084846862689705207</v>
+        <v>0.00036901567411752123</v>
       </c>
       <c r="R12">
-        <v>-0.00085915714661654436</v>
+        <v>7.946584800551978e-005</v>
       </c>
       <c r="S12">
-        <v>-0.00046619925224401185</v>
+        <v>-6.9447777617284002e-005</v>
       </c>
       <c r="T12">
-        <v>-5.3323372908775342e-005</v>
+        <v>0.00067906434791573729</v>
       </c>
       <c r="U12">
-        <v>0.00075113842343740357</v>
+        <v>0.00022186943271059991</v>
       </c>
       <c r="V12">
-        <v>0.00020299086774926191</v>
+        <v>0.00021121108277495773</v>
       </c>
       <c r="W12">
-        <v>0.00019425608418731567</v>
+        <v>0.00017325042355315529</v>
       </c>
       <c r="X12">
-        <v>0.00016961756555156136</v>
+        <v>4.4030040046096779e-005</v>
       </c>
       <c r="Y12">
-        <v>-6.7824766748861688e-005</v>
+        <v>-2.2169122959158477e-005</v>
       </c>
       <c r="Z12">
-        <v>-1.8624746291118655e-005</v>
+        <v>0.00096910402301362674</v>
       </c>
       <c r="AA12">
-        <v>0.00089117882584778432</v>
+        <v>0.00013988505826627502</v>
       </c>
       <c r="AB12">
-        <v>0.00015984243695851537</v>
+        <v>0.00015554595827289093</v>
       </c>
       <c r="AC12">
-        <v>0.00015276095428486906</v>
+        <v>0.00021232101009288336</v>
       </c>
       <c r="AD12">
-        <v>0.00020927702742451858</v>
+        <v>0.00019679202569056144</v>
       </c>
       <c r="AE12">
-        <v>0.00023131173692410751</v>
+        <v>0.00020517669905663826</v>
       </c>
       <c r="AF12">
-        <v>0.0002207292658957643</v>
+        <v>-4.9021864001511941e-005</v>
       </c>
       <c r="AG12">
-        <v>-3.7547916502796498e-005</v>
+        <v>-0.00034537691236294701</v>
       </c>
       <c r="AH12">
-        <v>-0.00027870482722584886</v>
+        <v>-0.00031356053569504263</v>
       </c>
       <c r="AI12">
-        <v>-0.00025642724126674079</v>
+        <v>-7.2145239984655433e-005</v>
       </c>
       <c r="AJ12">
-        <v>-8.7804087075625764e-005</v>
+        <v>0.00011089309233427985</v>
       </c>
       <c r="AK12">
-        <v>0.0001241885259186776</v>
+        <v>0.003083552768238876</v>
       </c>
       <c r="AL12">
-        <v>0.0028899975583858394</v>
-      </c>
-      <c r="AM12">
-        <v>0.0034055267868486018</v>
+        <v>0.0040992740004984918</v>
       </c>
     </row>
     <row r="13">
@@ -1896,118 +1857,115 @@
         <v>26</v>
       </c>
       <c r="B13">
-        <v>0.055597804714881384</v>
+        <v>0.1004223518716183</v>
       </c>
       <c r="C13">
-        <v>0.0017411285653893115</v>
+        <v>0.0024998240489301406</v>
       </c>
       <c r="D13">
-        <v>-9.9495523270052948e-005</v>
+        <v>-0.00011039133181760729</v>
       </c>
       <c r="E13">
-        <v>1.304116032090738e-006</v>
+        <v>1.407533756233143e-006</v>
       </c>
       <c r="F13">
-        <v>-1.11399856024788e-005</v>
+        <v>-1.1716278585893853e-005</v>
       </c>
       <c r="G13">
-        <v>-1.3308363103015295e-005</v>
+        <v>-1.3704425154398655e-005</v>
       </c>
       <c r="H13">
-        <v>-0.00033557454665997103</v>
+        <v>-0.00024341367877990234</v>
       </c>
       <c r="I13">
-        <v>0.001207096741080383</v>
+        <v>0.0011450639612123194</v>
       </c>
       <c r="J13">
-        <v>-0.0017009830834254676</v>
+        <v>-0.0018537725669807814</v>
       </c>
       <c r="K13">
-        <v>0.001591587028870513</v>
+        <v>0.0014685333092138062</v>
       </c>
       <c r="L13">
-        <v>0.0021656610802906354</v>
+        <v>0.0019928657707270719</v>
       </c>
       <c r="M13">
-        <v>0.0026035985994619991</v>
+        <v>0.00243646048019831</v>
       </c>
       <c r="N13">
-        <v>0.0031653830280201894</v>
+        <v>0.0029480246505267311</v>
       </c>
       <c r="O13">
-        <v>0.00011306154219092824</v>
+        <v>0.00012914402419098069</v>
       </c>
       <c r="P13">
-        <v>5.0235008408798136e-005</v>
+        <v>2.2060506415521492e-005</v>
       </c>
       <c r="Q13">
-        <v>-0.0011851881455553345</v>
+        <v>0.00039860108770974241</v>
       </c>
       <c r="R13">
-        <v>-0.00084498543918273838</v>
+        <v>-0.00024261828729805541</v>
       </c>
       <c r="S13">
-        <v>-0.00042620553334810947</v>
+        <v>-4.4905982813304621e-006</v>
       </c>
       <c r="T13">
-        <v>7.3799827864571535e-006</v>
+        <v>0.00069211985730013208</v>
       </c>
       <c r="U13">
-        <v>0.00077752310454945776</v>
+        <v>-0.00010119932177598412</v>
       </c>
       <c r="V13">
-        <v>-0.00011098077868122639</v>
+        <v>-3.1840166746726392e-005</v>
       </c>
       <c r="W13">
-        <v>-4.3713465726411287e-005</v>
+        <v>-0.00010609390933020687</v>
       </c>
       <c r="X13">
-        <v>-0.00011600144743554217</v>
+        <v>-0.000109379057276265</v>
       </c>
       <c r="Y13">
-        <v>-0.0001970910248080855</v>
+        <v>-0.00023580220127711153</v>
       </c>
       <c r="Z13">
-        <v>-0.00022821500695664011</v>
+        <v>0.00014268890174724282</v>
       </c>
       <c r="AA13">
-        <v>7.5889932605172983e-005</v>
+        <v>-6.7616915027152733e-005</v>
       </c>
       <c r="AB13">
-        <v>-4.4674775596068069e-005</v>
+        <v>-8.7069862596883573e-005</v>
       </c>
       <c r="AC13">
-        <v>-7.1650648008393994e-005</v>
+        <v>-3.3623293024817613e-005</v>
       </c>
       <c r="AD13">
-        <v>-2.8534753706098166e-005</v>
+        <v>-8.0590389062734462e-005</v>
       </c>
       <c r="AE13">
-        <v>-5.3242901788881717e-005</v>
+        <v>6.8534125630500447e-005</v>
       </c>
       <c r="AF13">
-        <v>9.1980433528481096e-005</v>
+        <v>4.5884060363310199e-006</v>
       </c>
       <c r="AG13">
-        <v>1.2948083191670457e-005</v>
+        <v>-9.8140343837553731e-005</v>
       </c>
       <c r="AH13">
-        <v>-4.8467231561043298e-005</v>
+        <v>-0.00018765639706114538</v>
       </c>
       <c r="AI13">
-        <v>-0.0001256434594235226</v>
+        <v>-0.00015072067519570492</v>
       </c>
       <c r="AJ13">
-        <v>-0.00015933562142264428</v>
+        <v>-6.1731432260778369e-005</v>
       </c>
       <c r="AK13">
-        <v>-5.3180075123619025e-005</v>
+        <v>0.0007289240914948817</v>
       </c>
       <c r="AL13">
-        <v>0.00052096746028740867</v>
-      </c>
-      <c r="AM13">
-        <v>0.00048887595754341408</v>
+        <v>0.00090945056340335784</v>
       </c>
     </row>
     <row r="14">
@@ -2015,118 +1973,115 @@
         <v>27</v>
       </c>
       <c r="B14">
-        <v>-0.071238216903370538</v>
+        <v>-0.086822838444699943</v>
       </c>
       <c r="C14">
-        <v>0.00035983244909435896</v>
+        <v>0.00035933179253314182</v>
       </c>
       <c r="D14">
-        <v>-3.7441546717449778e-005</v>
+        <v>-3.815443439177731e-005</v>
       </c>
       <c r="E14">
-        <v>3.4276583677961895e-007</v>
+        <v>3.5663546352233272e-007</v>
       </c>
       <c r="F14">
-        <v>-3.0741921896188944e-006</v>
+        <v>-3.4036825970215676e-006</v>
       </c>
       <c r="G14">
-        <v>-2.6634375283017533e-006</v>
+        <v>-2.329262762653658e-006</v>
       </c>
       <c r="H14">
-        <v>0.00011886030616974281</v>
+        <v>0.0001076567738074946</v>
       </c>
       <c r="I14">
-        <v>0.00011658934943760391</v>
+        <v>0.00011569640792940953</v>
       </c>
       <c r="J14">
-        <v>-0.00037916909427463026</v>
+        <v>-0.00037441032905224047</v>
       </c>
       <c r="K14">
-        <v>-0.00021610883532231732</v>
+        <v>-0.00021847746608245466</v>
       </c>
       <c r="L14">
-        <v>-8.1126396499593245e-005</v>
+        <v>-6.3787894216452802e-005</v>
       </c>
       <c r="M14">
-        <v>1.2288848817269593e-005</v>
+        <v>3.0343330767699259e-005</v>
       </c>
       <c r="N14">
-        <v>0.00011306154219092824</v>
+        <v>0.00012914402419098069</v>
       </c>
       <c r="O14">
-        <v>0.00033722331247687006</v>
+        <v>0.00033765366135622232</v>
       </c>
       <c r="P14">
-        <v>-0.00019712295215456525</v>
+        <v>-0.00018569450285125066</v>
       </c>
       <c r="Q14">
-        <v>8.6577998330836193e-005</v>
+        <v>0.00012461470677450963</v>
       </c>
       <c r="R14">
-        <v>3.2463401021254931e-005</v>
+        <v>6.0023707291430642e-005</v>
       </c>
       <c r="S14">
-        <v>0.00012558635782118302</v>
+        <v>9.720859063754657e-006</v>
       </c>
       <c r="T14">
-        <v>4.5231006806614369e-006</v>
+        <v>-9.3679197758314263e-005</v>
       </c>
       <c r="U14">
-        <v>-0.00010360861380155785</v>
+        <v>-0.00016221850859836158</v>
       </c>
       <c r="V14">
-        <v>-0.00015060323746151805</v>
+        <v>-0.00014674446367419946</v>
       </c>
       <c r="W14">
-        <v>-0.00013661106386636001</v>
+        <v>-0.00016526403002731558</v>
       </c>
       <c r="X14">
-        <v>-0.00015498900201568668</v>
+        <v>-0.00015547688599463</v>
       </c>
       <c r="Y14">
-        <v>-0.00011409197507376525</v>
+        <v>-0.00017300669066426546</v>
       </c>
       <c r="Z14">
-        <v>-0.0001580226207004052</v>
+        <v>-9.0688177183811795e-005</v>
       </c>
       <c r="AA14">
-        <v>-8.3557815764855026e-005</v>
+        <v>-0.0001624507531684933</v>
       </c>
       <c r="AB14">
-        <v>-0.0001459229403139331</v>
+        <v>-0.00014976798280946061</v>
       </c>
       <c r="AC14">
-        <v>-9.6854730497470786e-005</v>
+        <v>-9.1021842269327114e-005</v>
       </c>
       <c r="AD14">
-        <v>-8.2488468880938633e-005</v>
+        <v>-6.813341992730943e-005</v>
       </c>
       <c r="AE14">
-        <v>-6.5754985739405636e-005</v>
+        <v>-0.00019539853167959694</v>
       </c>
       <c r="AF14">
-        <v>-0.00018327013574199926</v>
+        <v>1.7860125300843399e-005</v>
       </c>
       <c r="AG14">
-        <v>1.2654912550386738e-005</v>
+        <v>-5.1172471083111583e-005</v>
       </c>
       <c r="AH14">
-        <v>-6.4173155977544083e-005</v>
+        <v>-2.2621205408135446e-005</v>
       </c>
       <c r="AI14">
-        <v>-2.4310245680168852e-005</v>
+        <v>-0.00011815262586697151</v>
       </c>
       <c r="AJ14">
-        <v>-0.00010962948838037818</v>
+        <v>-0.0002008529690260274</v>
       </c>
       <c r="AK14">
-        <v>-0.00020011437162407896</v>
+        <v>-3.8619813065707796e-005</v>
       </c>
       <c r="AL14">
-        <v>-5.5309452233983248e-005</v>
-      </c>
-      <c r="AM14">
-        <v>0.00039824274032360715</v>
+        <v>4.3470608544697587e-005</v>
       </c>
     </row>
     <row r="15">
@@ -2134,118 +2089,115 @@
         <v>28</v>
       </c>
       <c r="B15">
-        <v>0.15494825660361963</v>
+        <v>0.16788462988818506</v>
       </c>
       <c r="C15">
-        <v>2.5682801096006984e-005</v>
+        <v>1.0113937214667327e-006</v>
       </c>
       <c r="D15">
-        <v>-7.965909061907529e-005</v>
+        <v>-7.2795937571410493e-005</v>
       </c>
       <c r="E15">
-        <v>1.4867623043410641e-006</v>
+        <v>1.3797988040752383e-006</v>
       </c>
       <c r="F15">
-        <v>-7.9186546998027672e-007</v>
+        <v>-5.1477405488378426e-007</v>
       </c>
       <c r="G15">
-        <v>4.5349758374722388e-008</v>
+        <v>-1.2336917663742062e-007</v>
       </c>
       <c r="H15">
-        <v>-0.00016258252428948114</v>
+        <v>-0.0001422553832980845</v>
       </c>
       <c r="I15">
-        <v>0.00019851202789831137</v>
+        <v>0.00020508342396619042</v>
       </c>
       <c r="J15">
-        <v>-5.64259620386002e-005</v>
+        <v>-9.5999728761143486e-005</v>
       </c>
       <c r="K15">
-        <v>7.3163995802980565e-005</v>
+        <v>5.2407980440579609e-005</v>
       </c>
       <c r="L15">
-        <v>3.3133869317861561e-005</v>
+        <v>1.6273946601051163e-006</v>
       </c>
       <c r="M15">
-        <v>2.1602949602143793e-005</v>
+        <v>-9.0521128922805465e-006</v>
       </c>
       <c r="N15">
-        <v>5.0235008408798136e-005</v>
+        <v>2.2060506415521492e-005</v>
       </c>
       <c r="O15">
-        <v>-0.00019712295215456525</v>
+        <v>-0.00018569450285125066</v>
       </c>
       <c r="P15">
-        <v>0.00070908677712240272</v>
+        <v>0.00069275890243811135</v>
       </c>
       <c r="Q15">
-        <v>-3.7842421926537946e-005</v>
+        <v>3.8541370523724443e-005</v>
       </c>
       <c r="R15">
-        <v>3.4932905081316199e-005</v>
+        <v>-7.2475923723660049e-005</v>
       </c>
       <c r="S15">
-        <v>9.9230926284532567e-005</v>
+        <v>2.4637317800909549e-005</v>
       </c>
       <c r="T15">
-        <v>2.951295908471321e-005</v>
+        <v>-7.474233715450982e-005</v>
       </c>
       <c r="U15">
-        <v>-6.843485109927873e-005</v>
+        <v>-2.2335534111341613e-005</v>
       </c>
       <c r="V15">
-        <v>-2.5907489369842498e-005</v>
+        <v>-5.1352990622851069e-005</v>
       </c>
       <c r="W15">
-        <v>-5.5530839967479949e-005</v>
+        <v>-3.8218555959610345e-005</v>
       </c>
       <c r="X15">
-        <v>-3.9868680777276313e-005</v>
+        <v>-5.3711791986062474e-005</v>
       </c>
       <c r="Y15">
-        <v>-0.00010800958124315466</v>
+        <v>-3.2289573827664288e-005</v>
       </c>
       <c r="Z15">
-        <v>-3.645117398613652e-005</v>
+        <v>-0.00013012730981569012</v>
       </c>
       <c r="AA15">
-        <v>-0.00012885382009784478</v>
+        <v>-3.3265604737786351e-005</v>
       </c>
       <c r="AB15">
-        <v>-3.8397214794650835e-005</v>
+        <v>-2.4569788062412969e-005</v>
       </c>
       <c r="AC15">
-        <v>-6.7622387320927661e-005</v>
+        <v>-0.00011896915164282584</v>
       </c>
       <c r="AD15">
-        <v>-0.00011314137217187423</v>
+        <v>-0.00010895520225444251</v>
       </c>
       <c r="AE15">
-        <v>-0.00010194100135895608</v>
+        <v>-6.2830049325270559e-005</v>
       </c>
       <c r="AF15">
-        <v>-6.6273774619723515e-005</v>
+        <v>2.6914162160587055e-005</v>
       </c>
       <c r="AG15">
-        <v>3.0839067638836617e-005</v>
+        <v>7.3090305524119533e-005</v>
       </c>
       <c r="AH15">
-        <v>9.7030238788692417e-005</v>
+        <v>6.7007874260891387e-005</v>
       </c>
       <c r="AI15">
-        <v>7.2168682090197723e-005</v>
+        <v>8.2514014695242639e-005</v>
       </c>
       <c r="AJ15">
-        <v>8.1472330471192615e-005</v>
+        <v>3.3927801326661394e-005</v>
       </c>
       <c r="AK15">
-        <v>4.9074531602562288e-005</v>
+        <v>-0.0001540537768883164</v>
       </c>
       <c r="AL15">
-        <v>-0.00013130917894927551</v>
-      </c>
-      <c r="AM15">
-        <v>-0.0012331357582365326</v>
+        <v>-0.00094907875100946014</v>
       </c>
     </row>
     <row r="16">
@@ -2253,118 +2205,115 @@
         <v>29</v>
       </c>
       <c r="B16">
-        <v>0.28124141435405803</v>
+        <v>0.0061753723678480031</v>
       </c>
       <c r="C16">
-        <v>0.0102315829392424</v>
+        <v>0.00049670434483377367</v>
       </c>
       <c r="D16">
-        <v>-0.00032617901722270526</v>
+        <v>-3.7356494079785656e-005</v>
       </c>
       <c r="E16">
-        <v>4.5468934853515149e-006</v>
+        <v>4.2759490528907412e-007</v>
       </c>
       <c r="F16">
-        <v>2.4658105482023052e-006</v>
+        <v>6.2981877157942972e-007</v>
       </c>
       <c r="G16">
-        <v>-6.0258932343264948e-007</v>
+        <v>1.0685483222414431e-006</v>
       </c>
       <c r="H16">
-        <v>0.0010955470431101288</v>
+        <v>0.00013685166363699882</v>
       </c>
       <c r="I16">
-        <v>-0.00088764034978694147</v>
+        <v>0.0001265646273506865</v>
       </c>
       <c r="J16">
-        <v>-0.0010291078527164205</v>
+        <v>-0.00038093747183944705</v>
       </c>
       <c r="K16">
-        <v>-0.00042066767075136504</v>
+        <v>-2.1166851585592062e-006</v>
       </c>
       <c r="L16">
-        <v>-0.00091763003509725887</v>
+        <v>0.00018597997617051835</v>
       </c>
       <c r="M16">
-        <v>-0.00084846862689705207</v>
+        <v>0.00036901567411752123</v>
       </c>
       <c r="N16">
-        <v>-0.0011851881455553345</v>
+        <v>0.00039860108770974241</v>
       </c>
       <c r="O16">
-        <v>8.6577998330836193e-005</v>
+        <v>0.00012461470677450963</v>
       </c>
       <c r="P16">
-        <v>-3.7842421926537946e-005</v>
+        <v>3.8541370523724443e-005</v>
       </c>
       <c r="Q16">
-        <v>0.01138583597155113</v>
+        <v>0.0026726657884742996</v>
       </c>
       <c r="R16">
-        <v>0.010700997545545425</v>
+        <v>0.00023460161614381387</v>
       </c>
       <c r="S16">
-        <v>0.01071406315808832</v>
+        <v>4.0396583050570956e-005</v>
       </c>
       <c r="T16">
-        <v>-6.4262800994156245e-005</v>
+        <v>-0.00015383907320849172</v>
       </c>
       <c r="U16">
-        <v>-0.00059785059801118661</v>
+        <v>-2.2567480899933098e-005</v>
       </c>
       <c r="V16">
-        <v>-0.00015367429893801894</v>
+        <v>-0.00013737007142183161</v>
       </c>
       <c r="W16">
-        <v>4.5642886799761697e-005</v>
+        <v>-2.3936521514711416e-005</v>
       </c>
       <c r="X16">
-        <v>9.5995331025926917e-005</v>
+        <v>-0.00012946108255464984</v>
       </c>
       <c r="Y16">
-        <v>2.4413974239266231e-005</v>
+        <v>-0.00013495073394113942</v>
       </c>
       <c r="Z16">
-        <v>2.7729243894025844e-005</v>
+        <v>3.356846733454979e-005</v>
       </c>
       <c r="AA16">
-        <v>0.00046060705441066871</v>
+        <v>-0.0001104582948981032</v>
       </c>
       <c r="AB16">
-        <v>-5.1402781332026293e-005</v>
+        <v>-8.1067532035115333e-005</v>
       </c>
       <c r="AC16">
-        <v>0.00018307928558967512</v>
+        <v>-0.00010003898035512845</v>
       </c>
       <c r="AD16">
-        <v>0.00013008402825159392</v>
+        <v>-0.00012657168058127788</v>
       </c>
       <c r="AE16">
-        <v>-0.0001409239923375646</v>
+        <v>-0.00023614508635891638</v>
       </c>
       <c r="AF16">
-        <v>-0.00010696561359864291</v>
+        <v>5.9550340722653824e-005</v>
       </c>
       <c r="AG16">
-        <v>-5.7755553879237998e-005</v>
+        <v>4.123373150175983e-005</v>
       </c>
       <c r="AH16">
-        <v>-0.00017758135928915963</v>
+        <v>-4.5066907372377584e-005</v>
       </c>
       <c r="AI16">
-        <v>7.9531004010830603e-006</v>
+        <v>-0.00019753055342053782</v>
       </c>
       <c r="AJ16">
-        <v>0.00014254298045978482</v>
+        <v>-0.0001673118952549356</v>
       </c>
       <c r="AK16">
-        <v>0.0001895556842561616</v>
+        <v>0.00040364711340727449</v>
       </c>
       <c r="AL16">
-        <v>0.0015058865887626512</v>
-      </c>
-      <c r="AM16">
-        <v>0.00017465309214422658</v>
+        <v>-0.0032877227298290321</v>
       </c>
     </row>
     <row r="17">
@@ -2372,118 +2321,115 @@
         <v>30</v>
       </c>
       <c r="B17">
-        <v>0.27948014507763219</v>
+        <v>-0.028570397727055268</v>
       </c>
       <c r="C17">
-        <v>0.010199422762288841</v>
+        <v>0.00029322771365155502</v>
       </c>
       <c r="D17">
-        <v>-0.00031142883099790557</v>
+        <v>-9.6424489692912424e-006</v>
       </c>
       <c r="E17">
-        <v>4.3315929785775425e-006</v>
+        <v>1.680336718549152e-007</v>
       </c>
       <c r="F17">
-        <v>-1.3218507986615129e-008</v>
+        <v>1.9492088234102386e-006</v>
       </c>
       <c r="G17">
-        <v>1.8518830503332305e-006</v>
+        <v>-2.4121673474032823e-006</v>
       </c>
       <c r="H17">
-        <v>0.00057527362762469208</v>
+        <v>0.0005137867258616617</v>
       </c>
       <c r="I17">
-        <v>-0.00055032247543040295</v>
+        <v>-0.00032397927403205362</v>
       </c>
       <c r="J17">
-        <v>-0.00090875650235321722</v>
+        <v>-0.0001095571767722503</v>
       </c>
       <c r="K17">
-        <v>-0.0004151299276894555</v>
+        <v>1.4675730200645789e-005</v>
       </c>
       <c r="L17">
-        <v>-0.00092051597997631516</v>
+        <v>6.5609535066008537e-005</v>
       </c>
       <c r="M17">
-        <v>-0.00085915714661654436</v>
+        <v>7.946584800551978e-005</v>
       </c>
       <c r="N17">
-        <v>-0.00084498543918273838</v>
+        <v>-0.00024261828729805541</v>
       </c>
       <c r="O17">
-        <v>3.2463401021254931e-005</v>
+        <v>6.0023707291430642e-005</v>
       </c>
       <c r="P17">
-        <v>3.4932905081316199e-005</v>
+        <v>-7.2475923723660049e-005</v>
       </c>
       <c r="Q17">
-        <v>0.010700997545545425</v>
+        <v>0.00023460161614381387</v>
       </c>
       <c r="R17">
-        <v>0.010896423242198229</v>
+        <v>0.00082362455544611989</v>
       </c>
       <c r="S17">
-        <v>0.010681460673076579</v>
+        <v>-3.2461727831116624e-005</v>
       </c>
       <c r="T17">
-        <v>-2.8383978002302179e-005</v>
+        <v>1.806412128268023e-005</v>
       </c>
       <c r="U17">
-        <v>-0.0005822702487250221</v>
+        <v>0.0001394940465068653</v>
       </c>
       <c r="V17">
-        <v>-0.00031806157494344205</v>
+        <v>9.7667949925982016e-005</v>
       </c>
       <c r="W17">
-        <v>-7.0210911182595325e-005</v>
+        <v>0.00015301971938122097</v>
       </c>
       <c r="X17">
-        <v>-8.6787080050342502e-005</v>
+        <v>0.00013598312619678485</v>
       </c>
       <c r="Y17">
-        <v>-0.00011275815165588644</v>
+        <v>0.00015245295686200659</v>
       </c>
       <c r="Z17">
-        <v>-0.00014338969878311758</v>
+        <v>0.00054563069990100225</v>
       </c>
       <c r="AA17">
-        <v>-0.00014329477903666978</v>
+        <v>4.7969192084206777e-005</v>
       </c>
       <c r="AB17">
-        <v>-0.00011025566717806461</v>
+        <v>0.00020513423056947279</v>
       </c>
       <c r="AC17">
-        <v>-4.2544086228771564e-005</v>
+        <v>0.0003284185756094835</v>
       </c>
       <c r="AD17">
-        <v>-0.00022099665661149456</v>
+        <v>3.7555622515827747e-005</v>
       </c>
       <c r="AE17">
-        <v>-0.00020154467741714279</v>
+        <v>8.748847568642356e-005</v>
       </c>
       <c r="AF17">
-        <v>-0.00020517319066285476</v>
+        <v>-3.1293185513626155e-005</v>
       </c>
       <c r="AG17">
-        <v>-2.3421865775083859e-005</v>
+        <v>-0.00016126023072227601</v>
       </c>
       <c r="AH17">
-        <v>-7.1412653764946557e-006</v>
+        <v>-0.00014607868310096154</v>
       </c>
       <c r="AI17">
-        <v>0.00016203259298294779</v>
+        <v>-8.2136315290901583e-005</v>
       </c>
       <c r="AJ17">
-        <v>0.00021026214061750648</v>
+        <v>5.6853497491108306e-005</v>
       </c>
       <c r="AK17">
-        <v>0.00010601426602502208</v>
+        <v>0.0012600189609595931</v>
       </c>
       <c r="AL17">
-        <v>9.6809391473596379e-005</v>
-      </c>
-      <c r="AM17">
-        <v>-0.0024304330040109401</v>
+        <v>0.0020326671694665009</v>
       </c>
     </row>
     <row r="18">
@@ -2491,118 +2437,115 @@
         <v>31</v>
       </c>
       <c r="B18">
-        <v>0.27035084560392331</v>
+        <v>0.0044217377181533062</v>
       </c>
       <c r="C18">
-        <v>0.010447853876029464</v>
+        <v>-0.00011888182959127831</v>
       </c>
       <c r="D18">
-        <v>-0.00035617484726398088</v>
+        <v>-9.5251835126580059e-006</v>
       </c>
       <c r="E18">
-        <v>4.8908514038084667e-006</v>
+        <v>1.6086958889698568e-007</v>
       </c>
       <c r="F18">
-        <v>1.0355829237963498e-006</v>
+        <v>-7.6099522689724955e-007</v>
       </c>
       <c r="G18">
-        <v>3.3710789857197037e-006</v>
+        <v>1.2243568445699281e-006</v>
       </c>
       <c r="H18">
-        <v>0.00067333774121396779</v>
+        <v>4.0060671806974538e-005</v>
       </c>
       <c r="I18">
-        <v>-0.00043129017231416096</v>
+        <v>-5.3409189011997924e-005</v>
       </c>
       <c r="J18">
-        <v>-0.0012163947045443311</v>
+        <v>0.00012710126904816034</v>
       </c>
       <c r="K18">
-        <v>-0.00035363258624349607</v>
+        <v>-2.7615825078436737e-005</v>
       </c>
       <c r="L18">
-        <v>-0.00068552240126297948</v>
+        <v>-5.2002625690307014e-005</v>
       </c>
       <c r="M18">
-        <v>-0.00046619925224401185</v>
+        <v>-6.9447777617284002e-005</v>
       </c>
       <c r="N18">
-        <v>-0.00042620553334810947</v>
+        <v>-4.4905982813304621e-006</v>
       </c>
       <c r="O18">
-        <v>0.00012558635782118302</v>
+        <v>9.720859063754657e-006</v>
       </c>
       <c r="P18">
-        <v>9.9230926284532567e-005</v>
+        <v>2.4637317800909549e-005</v>
       </c>
       <c r="Q18">
-        <v>0.01071406315808832</v>
+        <v>4.0396583050570956e-005</v>
       </c>
       <c r="R18">
-        <v>0.010681460673076579</v>
+        <v>-3.2461727831116624e-005</v>
       </c>
       <c r="S18">
-        <v>0.013136588447033633</v>
+        <v>0.0001314469618547468</v>
       </c>
       <c r="T18">
-        <v>1.7528150953416378e-005</v>
+        <v>-1.2627528594437941e-005</v>
       </c>
       <c r="U18">
-        <v>-0.00071881651587655637</v>
+        <v>-6.4522130946138105e-005</v>
       </c>
       <c r="V18">
-        <v>-0.00031662691859479748</v>
+        <v>-7.1180565058700466e-005</v>
       </c>
       <c r="W18">
-        <v>-0.00018833360224259558</v>
+        <v>-6.8970063170110106e-005</v>
       </c>
       <c r="X18">
-        <v>-9.4599885276511718e-005</v>
+        <v>-4.9259729540188524e-005</v>
       </c>
       <c r="Y18">
-        <v>-0.00029359268963457391</v>
+        <v>-4.4280531223252293e-005</v>
       </c>
       <c r="Z18">
-        <v>-0.0002508157824914572</v>
+        <v>-0.00017373120861415361</v>
       </c>
       <c r="AA18">
-        <v>-0.00010162770774389124</v>
+        <v>-7.0291530293906329e-005</v>
       </c>
       <c r="AB18">
-        <v>-0.00020341667428457326</v>
+        <v>-7.0664859773725535e-005</v>
       </c>
       <c r="AC18">
-        <v>-0.0001251591646184891</v>
+        <v>-0.00010260146132290903</v>
       </c>
       <c r="AD18">
-        <v>-0.00029691637225277238</v>
+        <v>-9.2692278011749811e-005</v>
       </c>
       <c r="AE18">
-        <v>-0.00029953254315802347</v>
+        <v>-5.247179388989491e-005</v>
       </c>
       <c r="AF18">
-        <v>-0.00040533842495678058</v>
+        <v>0.00014427981051894279</v>
       </c>
       <c r="AG18">
-        <v>3.9084820280812236e-005</v>
+        <v>0.00023991112119895949</v>
       </c>
       <c r="AH18">
-        <v>7.065540882063813e-005</v>
+        <v>3.0318174977662232e-006</v>
       </c>
       <c r="AI18">
-        <v>0.00014888319302826594</v>
+        <v>-1.3490536425988381e-005</v>
       </c>
       <c r="AJ18">
-        <v>2.6178915629178779e-005</v>
+        <v>-4.166738257455364e-005</v>
       </c>
       <c r="AK18">
-        <v>-3.1948945107821824e-005</v>
+        <v>-0.00036338975652421696</v>
       </c>
       <c r="AL18">
-        <v>0.00044073173008572428</v>
-      </c>
-      <c r="AM18">
-        <v>-0.0058380059149684693</v>
+        <v>-0.0099010743776852192</v>
       </c>
     </row>
     <row r="19">
@@ -2610,118 +2553,115 @@
         <v>32</v>
       </c>
       <c r="B19">
-        <v>0.0037471125442778415</v>
+        <v>0.10563891621055886</v>
       </c>
       <c r="C19">
-        <v>-0.00014198997117942846</v>
+        <v>0.0010199109295059995</v>
       </c>
       <c r="D19">
-        <v>-1.1337993431873809e-005</v>
+        <v>2.9250763117061058e-005</v>
       </c>
       <c r="E19">
-        <v>1.8955816381488192e-007</v>
+        <v>-4.9421886907398326e-007</v>
       </c>
       <c r="F19">
-        <v>-8.4881199299117394e-007</v>
+        <v>8.6450308998339418e-006</v>
       </c>
       <c r="G19">
-        <v>1.2885670211706606e-006</v>
+        <v>4.2043462389814579e-006</v>
       </c>
       <c r="H19">
-        <v>3.2961652580161911e-005</v>
+        <v>0.00010029412965184243</v>
       </c>
       <c r="I19">
-        <v>-5.1320804953352336e-005</v>
+        <v>-2.8388705261737994e-006</v>
       </c>
       <c r="J19">
-        <v>0.00012995542925907226</v>
+        <v>-0.00055007105061917732</v>
       </c>
       <c r="K19">
-        <v>-2.1727292845972831e-005</v>
+        <v>0.00032516273591916387</v>
       </c>
       <c r="L19">
-        <v>-4.0108910420128815e-005</v>
+        <v>0.00056753835923690555</v>
       </c>
       <c r="M19">
-        <v>-5.3323372908775342e-005</v>
+        <v>0.00067906434791573729</v>
       </c>
       <c r="N19">
-        <v>7.3799827864571535e-006</v>
+        <v>0.00069211985730013208</v>
       </c>
       <c r="O19">
-        <v>4.5231006806614369e-006</v>
+        <v>-9.3679197758314263e-005</v>
       </c>
       <c r="P19">
-        <v>2.951295908471321e-005</v>
+        <v>-7.474233715450982e-005</v>
       </c>
       <c r="Q19">
-        <v>-6.4262800994156245e-005</v>
+        <v>-0.00015383907320849172</v>
       </c>
       <c r="R19">
-        <v>-2.8383978002302179e-005</v>
+        <v>1.806412128268023e-005</v>
       </c>
       <c r="S19">
-        <v>1.7528150953416378e-005</v>
+        <v>-1.2627528594437941e-005</v>
       </c>
       <c r="T19">
-        <v>0.00013304849712239249</v>
+        <v>0.0011179132437429988</v>
       </c>
       <c r="U19">
-        <v>-6.2539378192445804e-006</v>
+        <v>8.7577718951600299e-005</v>
       </c>
       <c r="V19">
-        <v>-5.8257147776617401e-005</v>
+        <v>0.00014782151443167789</v>
       </c>
       <c r="W19">
-        <v>-7.0163784819032935e-005</v>
+        <v>0.0001202127410452247</v>
       </c>
       <c r="X19">
-        <v>-6.7873188773793234e-005</v>
+        <v>0.00014235436072627922</v>
       </c>
       <c r="Y19">
-        <v>-5.5339687956407939e-005</v>
+        <v>8.5612186337318615e-005</v>
       </c>
       <c r="Z19">
-        <v>-4.2825643406315013e-005</v>
+        <v>0.0001822314797555488</v>
       </c>
       <c r="AA19">
-        <v>-0.00016792834308000833</v>
+        <v>7.0988986393154133e-005</v>
       </c>
       <c r="AB19">
-        <v>-6.6733917280000789e-005</v>
+        <v>0.00012793728228741431</v>
       </c>
       <c r="AC19">
-        <v>-7.6464906383686901e-005</v>
+        <v>5.6903460382430712e-005</v>
       </c>
       <c r="AD19">
-        <v>-9.9972528699135074e-005</v>
+        <v>0.00012808155560715189</v>
       </c>
       <c r="AE19">
-        <v>-8.8852888139570726e-005</v>
+        <v>0.00016609261590552738</v>
       </c>
       <c r="AF19">
-        <v>-4.9276418980819664e-005</v>
+        <v>-1.069406068963177e-005</v>
       </c>
       <c r="AG19">
-        <v>0.00014613747172832964</v>
+        <v>4.1218898197605686e-006</v>
       </c>
       <c r="AH19">
-        <v>0.0002423547939751497</v>
+        <v>-8.0479016927479654e-005</v>
       </c>
       <c r="AI19">
-        <v>2.5788455762674675e-006</v>
+        <v>-0.00012194659644551445</v>
       </c>
       <c r="AJ19">
-        <v>-1.087782945173978e-005</v>
+        <v>5.6130485394423487e-005</v>
       </c>
       <c r="AK19">
-        <v>-4.0352825567972067e-005</v>
+        <v>0.00014620496653568356</v>
       </c>
       <c r="AL19">
-        <v>-0.00036242969867932018</v>
-      </c>
-      <c r="AM19">
-        <v>-0.0099769069322157497</v>
+        <v>-0.00097122339958913631</v>
       </c>
     </row>
     <row r="20">
@@ -2729,118 +2669,115 @@
         <v>33</v>
       </c>
       <c r="B20">
-        <v>0.089728698039678909</v>
+        <v>-0.021358618079229806</v>
       </c>
       <c r="C20">
-        <v>0.00052990570015204268</v>
+        <v>-0.00076867217283246945</v>
       </c>
       <c r="D20">
-        <v>5.8479954139731451e-005</v>
+        <v>0.00010002735466648811</v>
       </c>
       <c r="E20">
-        <v>-9.0899788767463354e-007</v>
+        <v>-1.6460043078911126e-006</v>
       </c>
       <c r="F20">
-        <v>8.0994428268973417e-006</v>
+        <v>2.3840960654158269e-006</v>
       </c>
       <c r="G20">
-        <v>4.60083982283042e-006</v>
+        <v>-4.2902152116876318e-006</v>
       </c>
       <c r="H20">
-        <v>5.5767346755378381e-005</v>
+        <v>-0.00010528942491672935</v>
       </c>
       <c r="I20">
-        <v>3.6497749604622379e-005</v>
+        <v>9.625053137307306e-005</v>
       </c>
       <c r="J20">
-        <v>-0.00050011709093738914</v>
+        <v>0.00068504499296967892</v>
       </c>
       <c r="K20">
-        <v>0.00035005040671948478</v>
+        <v>0.00016448988830125791</v>
       </c>
       <c r="L20">
-        <v>0.00063252799218317061</v>
+        <v>3.2929314734775178e-005</v>
       </c>
       <c r="M20">
-        <v>0.00075113842343740357</v>
+        <v>0.00022186943271059991</v>
       </c>
       <c r="N20">
-        <v>0.00077752310454945776</v>
+        <v>-0.00010119932177598412</v>
       </c>
       <c r="O20">
-        <v>-0.00010360861380155785</v>
+        <v>-0.00016221850859836158</v>
       </c>
       <c r="P20">
-        <v>-6.843485109927873e-005</v>
+        <v>-2.2335534111341613e-005</v>
       </c>
       <c r="Q20">
-        <v>-0.00059785059801118661</v>
+        <v>-2.2567480899933098e-005</v>
       </c>
       <c r="R20">
-        <v>-0.0005822702487250221</v>
+        <v>0.0001394940465068653</v>
       </c>
       <c r="S20">
-        <v>-0.00071881651587655637</v>
+        <v>-6.4522130946138105e-005</v>
       </c>
       <c r="T20">
-        <v>-6.2539378192445804e-006</v>
+        <v>8.7577718951600299e-005</v>
       </c>
       <c r="U20">
-        <v>0.0011784191398641472</v>
+        <v>0.0056608810275070474</v>
       </c>
       <c r="V20">
-        <v>8.3809789491142935e-005</v>
+        <v>0.0018591409292627338</v>
       </c>
       <c r="W20">
-        <v>0.00013773385945759344</v>
+        <v>0.0019190569844707327</v>
       </c>
       <c r="X20">
-        <v>0.00011863786622654303</v>
+        <v>0.0018383992805826987</v>
       </c>
       <c r="Y20">
-        <v>0.00016037721342902254</v>
+        <v>0.0018329372944553405</v>
       </c>
       <c r="Z20">
-        <v>8.0825805621281192e-005</v>
+        <v>0.0022257051522154413</v>
       </c>
       <c r="AA20">
-        <v>0.00016537179180070496</v>
+        <v>0.001912795292793896</v>
       </c>
       <c r="AB20">
-        <v>7.7305988355607012e-005</v>
+        <v>0.001967264050686892</v>
       </c>
       <c r="AC20">
-        <v>9.0900753679595635e-005</v>
+        <v>0.0019459654629032539</v>
       </c>
       <c r="AD20">
-        <v>6.016099059067304e-005</v>
+        <v>0.0019234477107744766</v>
       </c>
       <c r="AE20">
-        <v>0.00013697508407044834</v>
+        <v>0.0019343044580812149</v>
       </c>
       <c r="AF20">
-        <v>0.00017068610340153188</v>
+        <v>-6.9094747112181216e-005</v>
       </c>
       <c r="AG20">
-        <v>-3.6427000747347316e-006</v>
+        <v>-2.800541060387512e-005</v>
       </c>
       <c r="AH20">
-        <v>2.080913430079585e-005</v>
+        <v>0.00020423697293106579</v>
       </c>
       <c r="AI20">
-        <v>-8.9286662794248574e-005</v>
+        <v>0.00059224413869626673</v>
       </c>
       <c r="AJ20">
-        <v>-0.00014094445270912111</v>
+        <v>0.0012144513629366524</v>
       </c>
       <c r="AK20">
-        <v>4.8919972715290717e-005</v>
+        <v>0.0018557043096712076</v>
       </c>
       <c r="AL20">
-        <v>7.3086596568319034e-005</v>
-      </c>
-      <c r="AM20">
-        <v>-0.0014223875737851589</v>
+        <v>0.0015986915576964179</v>
       </c>
     </row>
     <row r="21">
@@ -2848,118 +2785,115 @@
         <v>34</v>
       </c>
       <c r="B21">
-        <v>-0.023574008656411918</v>
+        <v>0.038533351018771783</v>
       </c>
       <c r="C21">
-        <v>-0.0011074628019153282</v>
+        <v>9.9843899083445348e-005</v>
       </c>
       <c r="D21">
-        <v>8.5971816482278564e-005</v>
+        <v>9.7696914191536038e-005</v>
       </c>
       <c r="E21">
-        <v>-1.4070648260265021e-006</v>
+        <v>-1.5113752313650239e-006</v>
       </c>
       <c r="F21">
-        <v>2.2097895872994584e-006</v>
+        <v>4.8115884531056557e-006</v>
       </c>
       <c r="G21">
-        <v>-4.155185354995559e-006</v>
+        <v>-4.7004202082222364e-006</v>
       </c>
       <c r="H21">
-        <v>-0.00016654237020553283</v>
+        <v>6.1315621847286546e-005</v>
       </c>
       <c r="I21">
-        <v>0.00016064438442527204</v>
+        <v>2.7722529029481345e-005</v>
       </c>
       <c r="J21">
-        <v>0.00070834421062997209</v>
+        <v>-6.766603457855825e-005</v>
       </c>
       <c r="K21">
-        <v>0.00015007271903986856</v>
+        <v>0.00012812622383470042</v>
       </c>
       <c r="L21">
-        <v>1.148014912290795e-005</v>
+        <v>9.2500495107306741e-005</v>
       </c>
       <c r="M21">
-        <v>0.00020299086774926191</v>
+        <v>0.00021121108277495773</v>
       </c>
       <c r="N21">
-        <v>-0.00011098077868122639</v>
+        <v>-3.1840166746726392e-005</v>
       </c>
       <c r="O21">
-        <v>-0.00015060323746151805</v>
+        <v>-0.00014674446367419946</v>
       </c>
       <c r="P21">
-        <v>-2.5907489369842498e-005</v>
+        <v>-5.1352990622851069e-005</v>
       </c>
       <c r="Q21">
-        <v>-0.00015367429893801894</v>
+        <v>-0.00013737007142183161</v>
       </c>
       <c r="R21">
-        <v>-0.00031806157494344205</v>
+        <v>9.7667949925982016e-005</v>
       </c>
       <c r="S21">
-        <v>-0.00031662691859479748</v>
+        <v>-7.1180565058700466e-005</v>
       </c>
       <c r="T21">
-        <v>-5.8257147776617401e-005</v>
+        <v>0.00014782151443167789</v>
       </c>
       <c r="U21">
-        <v>8.3809789491142935e-005</v>
+        <v>0.0018591409292627338</v>
       </c>
       <c r="V21">
-        <v>0.0056701951658992512</v>
+        <v>0.0029039977571822537</v>
       </c>
       <c r="W21">
-        <v>0.0018349828974136828</v>
+        <v>0.0018739630910457915</v>
       </c>
       <c r="X21">
-        <v>0.0018957504175654695</v>
+        <v>0.0018121681294245506</v>
       </c>
       <c r="Y21">
-        <v>0.0018132738673398534</v>
+        <v>0.0018020160735777568</v>
       </c>
       <c r="Z21">
-        <v>0.0018119136524288445</v>
+        <v>0.0020843157520594028</v>
       </c>
       <c r="AA21">
-        <v>0.0021955981502143149</v>
+        <v>0.0018547431115489821</v>
       </c>
       <c r="AB21">
-        <v>0.0018935755013667404</v>
+        <v>0.0019142122248394489</v>
       </c>
       <c r="AC21">
-        <v>0.0019424186431544477</v>
+        <v>0.0018925716503594219</v>
       </c>
       <c r="AD21">
-        <v>0.0019227344986453038</v>
+        <v>0.001859179841578501</v>
       </c>
       <c r="AE21">
-        <v>0.0019076429400642007</v>
+        <v>0.0018862661205086733</v>
       </c>
       <c r="AF21">
-        <v>0.0019090565111093919</v>
+        <v>-8.1414709880193694e-005</v>
       </c>
       <c r="AG21">
-        <v>-6.1797978299392184e-005</v>
+        <v>-0.00015782093667063616</v>
       </c>
       <c r="AH21">
-        <v>-2.446560032781501e-005</v>
+        <v>1.328343357181967e-005</v>
       </c>
       <c r="AI21">
-        <v>0.00019412403023791542</v>
+        <v>0.00048585264649225334</v>
       </c>
       <c r="AJ21">
-        <v>0.0005724794586272103</v>
+        <v>0.0010697430335632014</v>
       </c>
       <c r="AK21">
-        <v>0.0011834377782937802</v>
+        <v>0.0013332469138491758</v>
       </c>
       <c r="AL21">
-        <v>0.001832102022181187</v>
-      </c>
-      <c r="AM21">
-        <v>0.0016411661088852701</v>
+        <v>0.0020554803050226098</v>
       </c>
     </row>
     <row r="22">
@@ -2967,118 +2901,115 @@
         <v>35</v>
       </c>
       <c r="B22">
-        <v>0.048439955369987159</v>
+        <v>-0.031788219827850503</v>
       </c>
       <c r="C22">
-        <v>3.0193382082029617e-005</v>
+        <v>0.00033524910201420619</v>
       </c>
       <c r="D22">
-        <v>8.6724352162270094e-005</v>
+        <v>0.00015148120499576713</v>
       </c>
       <c r="E22">
-        <v>-1.336048458737508e-006</v>
+        <v>-2.2779225865855253e-006</v>
       </c>
       <c r="F22">
-        <v>4.4210011579929542e-006</v>
+        <v>3.6774430108213565e-006</v>
       </c>
       <c r="G22">
-        <v>-4.5305505278542616e-006</v>
+        <v>-3.0597444992348512e-006</v>
       </c>
       <c r="H22">
-        <v>3.5748213693306916e-005</v>
+        <v>5.3322173083817802e-005</v>
       </c>
       <c r="I22">
-        <v>4.7447159831332788e-005</v>
+        <v>9.3460319157949705e-005</v>
       </c>
       <c r="J22">
-        <v>-7.0992073392485612e-005</v>
+        <v>0.0003800076857157507</v>
       </c>
       <c r="K22">
-        <v>0.00010877662826730133</v>
+        <v>5.1012743587666192e-005</v>
       </c>
       <c r="L22">
-        <v>8.9784346590368879e-005</v>
+        <v>3.6926477130641574e-005</v>
       </c>
       <c r="M22">
-        <v>0.00019425608418731567</v>
+        <v>0.00017325042355315529</v>
       </c>
       <c r="N22">
-        <v>-4.3713465726411287e-005</v>
+        <v>-0.00010609390933020687</v>
       </c>
       <c r="O22">
-        <v>-0.00013661106386636001</v>
+        <v>-0.00016526403002731558</v>
       </c>
       <c r="P22">
-        <v>-5.5530839967479949e-005</v>
+        <v>-3.8218555959610345e-005</v>
       </c>
       <c r="Q22">
-        <v>4.5642886799761697e-005</v>
+        <v>-2.3936521514711416e-005</v>
       </c>
       <c r="R22">
-        <v>-7.0210911182595325e-005</v>
+        <v>0.00015301971938122097</v>
       </c>
       <c r="S22">
-        <v>-0.00018833360224259558</v>
+        <v>-6.8970063170110106e-005</v>
       </c>
       <c r="T22">
-        <v>-7.0163784819032935e-005</v>
+        <v>0.0001202127410452247</v>
       </c>
       <c r="U22">
-        <v>0.00013773385945759344</v>
+        <v>0.0019190569844707327</v>
       </c>
       <c r="V22">
-        <v>0.0018349828974136828</v>
+        <v>0.0018739630910457915</v>
       </c>
       <c r="W22">
-        <v>0.0028853275894578753</v>
+        <v>0.0033756487228512305</v>
       </c>
       <c r="X22">
-        <v>0.0018516568106324393</v>
+        <v>0.0018569111189023677</v>
       </c>
       <c r="Y22">
-        <v>0.0017854562147462142</v>
+        <v>0.0018432616468664869</v>
       </c>
       <c r="Z22">
-        <v>0.0017801767739322959</v>
+        <v>0.0022526077185054897</v>
       </c>
       <c r="AA22">
-        <v>0.0020612416626022197</v>
+        <v>0.0019050410418377075</v>
       </c>
       <c r="AB22">
-        <v>0.0018334389485025486</v>
+        <v>0.0019834305206509056</v>
       </c>
       <c r="AC22">
-        <v>0.0018886555966209644</v>
+        <v>0.0019719113567190309</v>
       </c>
       <c r="AD22">
-        <v>0.0018698057176101293</v>
+        <v>0.0019119262111984207</v>
       </c>
       <c r="AE22">
-        <v>0.001841631944655864</v>
+        <v>0.0019247589717999031</v>
       </c>
       <c r="AF22">
-        <v>0.0018622309679966918</v>
+        <v>-7.3788602868653645e-005</v>
       </c>
       <c r="AG22">
-        <v>-8.0056414420442713e-005</v>
+        <v>-0.00014837569300896051</v>
       </c>
       <c r="AH22">
-        <v>-0.00016046336404121266</v>
+        <v>-0.00014209814536660597</v>
       </c>
       <c r="AI22">
-        <v>1.4623108289534632e-005</v>
+        <v>0.00062447968276697083</v>
       </c>
       <c r="AJ22">
-        <v>0.00046588155042047853</v>
+        <v>0.0011006478529723179</v>
       </c>
       <c r="AK22">
-        <v>0.0010531376170443262</v>
+        <v>0.0018522942790446585</v>
       </c>
       <c r="AL22">
-        <v>0.0013275134412555449</v>
-      </c>
-      <c r="AM22">
-        <v>0.0022422053548026072</v>
+        <v>0.00083708268416976626</v>
       </c>
     </row>
     <row r="23">
@@ -3086,118 +3017,115 @@
         <v>36</v>
       </c>
       <c r="B23">
-        <v>-0.041355292465261345</v>
+        <v>0.064772105502824071</v>
       </c>
       <c r="C23">
-        <v>0.00025205799776496795</v>
+        <v>0.0002542012668357897</v>
       </c>
       <c r="D23">
-        <v>0.00013472511399825992</v>
+        <v>0.00015591486103541338</v>
       </c>
       <c r="E23">
-        <v>-2.0077848392030662e-006</v>
+        <v>-2.4279442505935095e-006</v>
       </c>
       <c r="F23">
-        <v>3.6529729111338584e-006</v>
+        <v>2.4271270391688767e-006</v>
       </c>
       <c r="G23">
-        <v>-2.9445526438273674e-006</v>
+        <v>-2.4433196165733625e-006</v>
       </c>
       <c r="H23">
-        <v>3.9597475021291122e-005</v>
+        <v>1.0231736943888079e-006</v>
       </c>
       <c r="I23">
-        <v>0.00011338948250712218</v>
+        <v>2.5625850678215843e-005</v>
       </c>
       <c r="J23">
-        <v>0.00040858019270463434</v>
+        <v>-7.4020544988011533e-005</v>
       </c>
       <c r="K23">
-        <v>5.3210594658557625e-005</v>
+        <v>7.5102046503341881e-005</v>
       </c>
       <c r="L23">
-        <v>3.5242119872064503e-005</v>
+        <v>3.508278580626118e-006</v>
       </c>
       <c r="M23">
-        <v>0.00016961756555156136</v>
+        <v>4.4030040046096779e-005</v>
       </c>
       <c r="N23">
-        <v>-0.00011600144743554217</v>
+        <v>-0.000109379057276265</v>
       </c>
       <c r="O23">
-        <v>-0.00015498900201568668</v>
+        <v>-0.00015547688599463</v>
       </c>
       <c r="P23">
-        <v>-3.9868680777276313e-005</v>
+        <v>-5.3711791986062474e-005</v>
       </c>
       <c r="Q23">
-        <v>9.5995331025926917e-005</v>
+        <v>-0.00012946108255464984</v>
       </c>
       <c r="R23">
-        <v>-8.6787080050342502e-005</v>
+        <v>0.00013598312619678485</v>
       </c>
       <c r="S23">
-        <v>-9.4599885276511718e-005</v>
+        <v>-4.9259729540188524e-005</v>
       </c>
       <c r="T23">
-        <v>-6.7873188773793234e-005</v>
+        <v>0.00014235436072627922</v>
       </c>
       <c r="U23">
-        <v>0.00011863786622654303</v>
+        <v>0.0018383992805826987</v>
       </c>
       <c r="V23">
-        <v>0.0018957504175654695</v>
+        <v>0.0018121681294245506</v>
       </c>
       <c r="W23">
-        <v>0.0018516568106324393</v>
+        <v>0.0018569111189023677</v>
       </c>
       <c r="X23">
-        <v>0.0033561540387908569</v>
+        <v>0.0033608982072781614</v>
       </c>
       <c r="Y23">
-        <v>0.001829871940711939</v>
+        <v>0.0018006741756848607</v>
       </c>
       <c r="Z23">
-        <v>0.001824212682348253</v>
+        <v>0.0020176874154114225</v>
       </c>
       <c r="AA23">
-        <v>0.0022289797472205548</v>
+        <v>0.0018529140743705269</v>
       </c>
       <c r="AB23">
-        <v>0.0018891387148021982</v>
+        <v>0.0018988313543409519</v>
       </c>
       <c r="AC23">
-        <v>0.0019669755571359799</v>
+        <v>0.001896946618750383</v>
       </c>
       <c r="AD23">
-        <v>0.0019515437354400192</v>
+        <v>0.0018376639034045792</v>
       </c>
       <c r="AE23">
-        <v>0.0018976065159970572</v>
+        <v>0.0018871044816416663</v>
       </c>
       <c r="AF23">
-        <v>0.0019019571104856216</v>
+        <v>-6.0230969855493805e-005</v>
       </c>
       <c r="AG23">
-        <v>-7.348242209479969e-005</v>
+        <v>-1.4933057935808671e-005</v>
       </c>
       <c r="AH23">
-        <v>-0.00014909826210742546</v>
+        <v>5.1566806203337068e-005</v>
       </c>
       <c r="AI23">
-        <v>-0.00012723979908432255</v>
+        <v>0.00048792132441952948</v>
       </c>
       <c r="AJ23">
-        <v>0.00060729061207093335</v>
+        <v>0.0010984911221362502</v>
       </c>
       <c r="AK23">
-        <v>0.0010822235155489822</v>
+        <v>0.0010068176402697609</v>
       </c>
       <c r="AL23">
-        <v>0.001833581487856372</v>
-      </c>
-      <c r="AM23">
-        <v>0.0011014995924897028</v>
+        <v>-0.00035028013161433023</v>
       </c>
     </row>
     <row r="24">
@@ -3205,118 +3133,115 @@
         <v>37</v>
       </c>
       <c r="B24">
-        <v>0.072845243231751178</v>
+        <v>0.027190868861844582</v>
       </c>
       <c r="C24">
-        <v>0.00019167420371769502</v>
+        <v>0.0011485613489293509</v>
       </c>
       <c r="D24">
-        <v>0.0001784627749928795</v>
+        <v>0.00016376817462691743</v>
       </c>
       <c r="E24">
-        <v>-2.7685251274408426e-006</v>
+        <v>-2.4522016072461152e-006</v>
       </c>
       <c r="F24">
-        <v>1.3547097494412623e-006</v>
+        <v>3.4114284080595614e-006</v>
       </c>
       <c r="G24">
-        <v>-2.7474816995351886e-006</v>
+        <v>-2.38893241984942e-006</v>
       </c>
       <c r="H24">
-        <v>4.3474083207095515e-005</v>
+        <v>-0.00010488322641709349</v>
       </c>
       <c r="I24">
-        <v>5.3550561024909879e-005</v>
+        <v>0.00012023779858716811</v>
       </c>
       <c r="J24">
-        <v>-0.00016681250310410654</v>
+        <v>-0.00099234758414382942</v>
       </c>
       <c r="K24">
-        <v>-7.544271015863131e-005</v>
+        <v>4.1714865828999196e-005</v>
       </c>
       <c r="L24">
-        <v>-0.00012409300974720907</v>
+        <v>-2.9575608927579205e-005</v>
       </c>
       <c r="M24">
-        <v>-6.7824766748861688e-005</v>
+        <v>-2.2169122959158477e-005</v>
       </c>
       <c r="N24">
-        <v>-0.0001970910248080855</v>
+        <v>-0.00023580220127711153</v>
       </c>
       <c r="O24">
-        <v>-0.00011409197507376525</v>
+        <v>-0.00017300669066426546</v>
       </c>
       <c r="P24">
-        <v>-0.00010800958124315466</v>
+        <v>-3.2289573827664288e-005</v>
       </c>
       <c r="Q24">
-        <v>2.4413974239266231e-005</v>
+        <v>-0.00013495073394113942</v>
       </c>
       <c r="R24">
-        <v>-0.00011275815165588644</v>
+        <v>0.00015245295686200659</v>
       </c>
       <c r="S24">
-        <v>-0.00029359268963457391</v>
+        <v>-4.4280531223252293e-005</v>
       </c>
       <c r="T24">
-        <v>-5.5339687956407939e-005</v>
+        <v>8.5612186337318615e-005</v>
       </c>
       <c r="U24">
-        <v>0.00016037721342902254</v>
+        <v>0.0018329372944553405</v>
       </c>
       <c r="V24">
-        <v>0.0018132738673398534</v>
+        <v>0.0018020160735777568</v>
       </c>
       <c r="W24">
-        <v>0.0017854562147462142</v>
+        <v>0.0018432616468664869</v>
       </c>
       <c r="X24">
-        <v>0.001829871940711939</v>
+        <v>0.0018006741756848607</v>
       </c>
       <c r="Y24">
-        <v>0.0035137509430400275</v>
+        <v>0.0032728464856861656</v>
       </c>
       <c r="Z24">
-        <v>0.0017756819340801616</v>
+        <v>0.0020245120832106853</v>
       </c>
       <c r="AA24">
-        <v>0.0019929199346297214</v>
+        <v>0.0018369250440353826</v>
       </c>
       <c r="AB24">
-        <v>0.00183456994750856</v>
+        <v>0.0018822998102729143</v>
       </c>
       <c r="AC24">
-        <v>0.001879348419157829</v>
+        <v>0.0018685294126952552</v>
       </c>
       <c r="AD24">
-        <v>0.001869699950968591</v>
+        <v>0.001823432850529258</v>
       </c>
       <c r="AE24">
-        <v>0.0018128962500671545</v>
+        <v>0.0018609015339981203</v>
       </c>
       <c r="AF24">
-        <v>0.001851837600131973</v>
+        <v>-5.8479465151153238e-005</v>
       </c>
       <c r="AG24">
-        <v>-6.1542679526740732e-005</v>
+        <v>2.2584090247459543e-005</v>
       </c>
       <c r="AH24">
-        <v>-6.1583855512882578e-005</v>
+        <v>-7.8491701891405814e-005</v>
       </c>
       <c r="AI24">
-        <v>1.5587797207983179e-006</v>
+        <v>0.00039237678988009872</v>
       </c>
       <c r="AJ24">
-        <v>0.00044944452169753111</v>
+        <v>0.0010532951890321633</v>
       </c>
       <c r="AK24">
-        <v>0.0010410031428158138</v>
+        <v>0.0012138140024918758</v>
       </c>
       <c r="AL24">
-        <v>0.00092339645879814872</v>
-      </c>
-      <c r="AM24">
-        <v>-6.4030839606421357e-005</v>
+        <v>-0.00083420667951310907</v>
       </c>
     </row>
     <row r="25">
@@ -3324,118 +3249,115 @@
         <v>38</v>
       </c>
       <c r="B25">
-        <v>0.025028004910651377</v>
+        <v>0.13508929737163061</v>
       </c>
       <c r="C25">
-        <v>0.0011008121017136514</v>
+        <v>0.00074899313178353015</v>
       </c>
       <c r="D25">
-        <v>0.00015364260354093582</v>
+        <v>0.00023104011681060292</v>
       </c>
       <c r="E25">
-        <v>-2.2859063054757216e-006</v>
+        <v>-3.6698382590131281e-006</v>
       </c>
       <c r="F25">
-        <v>3.2285176272676075e-006</v>
+        <v>1.0082272882256399e-005</v>
       </c>
       <c r="G25">
-        <v>-2.2486698792265617e-006</v>
+        <v>-1.3634444692037891e-005</v>
       </c>
       <c r="H25">
-        <v>-0.0001235650547236294</v>
+        <v>0.00051918324552543635</v>
       </c>
       <c r="I25">
-        <v>0.00015575580233343205</v>
+        <v>0.00020126442066449894</v>
       </c>
       <c r="J25">
-        <v>-0.0010819187583191196</v>
+        <v>-0.00071630488343343748</v>
       </c>
       <c r="K25">
-        <v>3.7186797125790836e-005</v>
+        <v>0.0002411140451282739</v>
       </c>
       <c r="L25">
-        <v>-3.1997367791196287e-005</v>
+        <v>0.00035881530777383958</v>
       </c>
       <c r="M25">
-        <v>-1.8624746291118655e-005</v>
+        <v>0.00096910402301362674</v>
       </c>
       <c r="N25">
-        <v>-0.00022821500695664011</v>
+        <v>0.00014268890174724282</v>
       </c>
       <c r="O25">
-        <v>-0.0001580226207004052</v>
+        <v>-9.0688177183811795e-005</v>
       </c>
       <c r="P25">
-        <v>-3.645117398613652e-005</v>
+        <v>-0.00013012730981569012</v>
       </c>
       <c r="Q25">
-        <v>2.7729243894025844e-005</v>
+        <v>3.356846733454979e-005</v>
       </c>
       <c r="R25">
-        <v>-0.00014338969878311758</v>
+        <v>0.00054563069990100225</v>
       </c>
       <c r="S25">
-        <v>-0.0002508157824914572</v>
+        <v>-0.00017373120861415361</v>
       </c>
       <c r="T25">
-        <v>-4.2825643406315013e-005</v>
+        <v>0.0001822314797555488</v>
       </c>
       <c r="U25">
-        <v>8.0825805621281192e-005</v>
+        <v>0.0022257051522154413</v>
       </c>
       <c r="V25">
-        <v>0.0018119136524288445</v>
+        <v>0.0020843157520594028</v>
       </c>
       <c r="W25">
-        <v>0.0017801767739322959</v>
+        <v>0.0022526077185054897</v>
       </c>
       <c r="X25">
-        <v>0.001824212682348253</v>
+        <v>0.0020176874154114225</v>
       </c>
       <c r="Y25">
-        <v>0.0017756819340801616</v>
+        <v>0.0020245120832106853</v>
       </c>
       <c r="Z25">
-        <v>0.0032660521999629591</v>
+        <v>0.0047946962091994262</v>
       </c>
       <c r="AA25">
-        <v>0.0020086467344272397</v>
+        <v>0.0020844540782809663</v>
       </c>
       <c r="AB25">
-        <v>0.0018180984222387095</v>
+        <v>0.0022759411718895574</v>
       </c>
       <c r="AC25">
-        <v>0.0018633938747233823</v>
+        <v>0.0021764611310518042</v>
       </c>
       <c r="AD25">
-        <v>0.0018522702834956363</v>
+        <v>0.0020787378323642199</v>
       </c>
       <c r="AE25">
-        <v>0.0018079705445605881</v>
+        <v>0.0020937782408174512</v>
       </c>
       <c r="AF25">
-        <v>0.0018376257676263566</v>
+        <v>-0.00014408431904570646</v>
       </c>
       <c r="AG25">
-        <v>-5.7049321145558635e-005</v>
+        <v>-0.00073929879812733115</v>
       </c>
       <c r="AH25">
-        <v>2.2803861424251976e-005</v>
+        <v>-0.00063263093883486013</v>
       </c>
       <c r="AI25">
-        <v>-7.8248246057880831e-005</v>
+        <v>0.00054771532522141344</v>
       </c>
       <c r="AJ25">
-        <v>0.00037506279914277074</v>
+        <v>0.00080382141040420099</v>
       </c>
       <c r="AK25">
-        <v>0.0010315650564605198</v>
+        <v>0.0053073350236214987</v>
       </c>
       <c r="AL25">
-        <v>0.0012200845725457501</v>
-      </c>
-      <c r="AM25">
-        <v>-0.00065833618555343615</v>
+        <v>0.0062611633868852228</v>
       </c>
     </row>
     <row r="26">
@@ -3443,118 +3365,115 @@
         <v>39</v>
       </c>
       <c r="B26">
-        <v>0.13801804762362699</v>
+        <v>0.027408885369360939</v>
       </c>
       <c r="C26">
-        <v>0.00060029698893082455</v>
+        <v>-4.5955709517460277e-005</v>
       </c>
       <c r="D26">
-        <v>0.00021545924894668302</v>
+        <v>0.00015391516887878798</v>
       </c>
       <c r="E26">
-        <v>-3.4221294103590246e-006</v>
+        <v>-2.329387002131441e-006</v>
       </c>
       <c r="F26">
-        <v>9.8500381987626435e-006</v>
+        <v>2.7490599463574994e-007</v>
       </c>
       <c r="G26">
-        <v>-1.3162899400323308e-005</v>
+        <v>-3.7931236235367004e-006</v>
       </c>
       <c r="H26">
-        <v>0.0005020151131680463</v>
+        <v>-0.0003721287412152701</v>
       </c>
       <c r="I26">
-        <v>0.00019989892680981119</v>
+        <v>0.00043812760120408225</v>
       </c>
       <c r="J26">
-        <v>-0.00073081431253175155</v>
+        <v>0.00014257303752827043</v>
       </c>
       <c r="K26">
-        <v>0.00020931618340061921</v>
+        <v>0.00010903687405521687</v>
       </c>
       <c r="L26">
-        <v>0.00031009742604268514</v>
+        <v>4.3008552664827021e-005</v>
       </c>
       <c r="M26">
-        <v>0.00089117882584778432</v>
+        <v>0.00013988505826627502</v>
       </c>
       <c r="N26">
-        <v>7.5889932605172983e-005</v>
+        <v>-6.7616915027152733e-005</v>
       </c>
       <c r="O26">
-        <v>-8.3557815764855026e-005</v>
+        <v>-0.0001624507531684933</v>
       </c>
       <c r="P26">
-        <v>-0.00012885382009784478</v>
+        <v>-3.3265604737786351e-005</v>
       </c>
       <c r="Q26">
-        <v>0.00046060705441066871</v>
+        <v>-0.0001104582948981032</v>
       </c>
       <c r="R26">
-        <v>-0.00014329477903666978</v>
+        <v>4.7969192084206777e-005</v>
       </c>
       <c r="S26">
-        <v>-0.00010162770774389124</v>
+        <v>-7.0291530293906329e-005</v>
       </c>
       <c r="T26">
-        <v>-0.00016792834308000833</v>
+        <v>7.0988986393154133e-005</v>
       </c>
       <c r="U26">
-        <v>0.00016537179180070496</v>
+        <v>0.001912795292793896</v>
       </c>
       <c r="V26">
-        <v>0.0021955981502143149</v>
+        <v>0.0018547431115489821</v>
       </c>
       <c r="W26">
-        <v>0.0020612416626022197</v>
+        <v>0.0019050410418377075</v>
       </c>
       <c r="X26">
-        <v>0.0022289797472205548</v>
+        <v>0.0018529140743705269</v>
       </c>
       <c r="Y26">
-        <v>0.0019929199346297214</v>
+        <v>0.0018369250440353826</v>
       </c>
       <c r="Z26">
-        <v>0.0020086467344272397</v>
+        <v>0.0020844540782809663</v>
       </c>
       <c r="AA26">
-        <v>0.0047278619262140428</v>
+        <v>0.0029556717373847041</v>
       </c>
       <c r="AB26">
-        <v>0.0020639868662480367</v>
+        <v>0.0019415041072444105</v>
       </c>
       <c r="AC26">
-        <v>0.0022475835433209586</v>
+        <v>0.0019284005631256468</v>
       </c>
       <c r="AD26">
-        <v>0.0021588279814631958</v>
+        <v>0.0018781895595058886</v>
       </c>
       <c r="AE26">
-        <v>0.0020607525154057657</v>
+        <v>0.001916853063242227</v>
       </c>
       <c r="AF26">
-        <v>0.002067077575224595</v>
+        <v>-7.1064037082577212e-005</v>
       </c>
       <c r="AG26">
-        <v>-0.000140504742674733</v>
+        <v>-0.00025048121641180329</v>
       </c>
       <c r="AH26">
-        <v>-0.00070927881202781492</v>
+        <v>-0.00011899993288583591</v>
       </c>
       <c r="AI26">
-        <v>-0.00060994808775402499</v>
+        <v>0.0004622755930847283</v>
       </c>
       <c r="AJ26">
-        <v>0.00052747675100903104</v>
+        <v>0.0014471396875052151</v>
       </c>
       <c r="AK26">
-        <v>0.00080031374260806421</v>
+        <v>0.0011588471591380423</v>
       </c>
       <c r="AL26">
-        <v>0.0052641329408566855</v>
-      </c>
-      <c r="AM26">
-        <v>0.0062824420735123664</v>
+        <v>0.0011646950095624917</v>
       </c>
     </row>
     <row r="27">
@@ -3562,118 +3481,115 @@
         <v>40</v>
       </c>
       <c r="B27">
-        <v>0.033415142458126906</v>
+        <v>0.063273413479129334</v>
       </c>
       <c r="C27">
-        <v>-0.00013417223288986755</v>
+        <v>0.00024187105804528088</v>
       </c>
       <c r="D27">
-        <v>0.00014408899750075884</v>
+        <v>0.00016588269486408154</v>
       </c>
       <c r="E27">
-        <v>-2.1575606670473814e-006</v>
+        <v>-2.5452449907154385e-006</v>
       </c>
       <c r="F27">
-        <v>5.0043655215772424e-007</v>
+        <v>3.469416830102173e-006</v>
       </c>
       <c r="G27">
-        <v>-3.5954298320892207e-006</v>
+        <v>-3.6845379686415348e-006</v>
       </c>
       <c r="H27">
-        <v>-0.00037101907844401408</v>
+        <v>-1.7790452162926219e-006</v>
       </c>
       <c r="I27">
-        <v>0.00046517043840930159</v>
+        <v>0.00015704120578152552</v>
       </c>
       <c r="J27">
-        <v>0.00012973320962810292</v>
+        <v>-7.3443682259383505e-005</v>
       </c>
       <c r="K27">
-        <v>0.00010088482246977656</v>
+        <v>6.9897023413304144e-005</v>
       </c>
       <c r="L27">
-        <v>4.6426937158933863e-005</v>
+        <v>4.7475844356725816e-005</v>
       </c>
       <c r="M27">
-        <v>0.00015984243695851537</v>
+        <v>0.00015554595827289093</v>
       </c>
       <c r="N27">
-        <v>-4.4674775596068069e-005</v>
+        <v>-8.7069862596883573e-005</v>
       </c>
       <c r="O27">
-        <v>-0.0001459229403139331</v>
+        <v>-0.00014976798280946061</v>
       </c>
       <c r="P27">
-        <v>-3.8397214794650835e-005</v>
+        <v>-2.4569788062412969e-005</v>
       </c>
       <c r="Q27">
-        <v>-5.1402781332026293e-005</v>
+        <v>-8.1067532035115333e-005</v>
       </c>
       <c r="R27">
-        <v>-0.00011025566717806461</v>
+        <v>0.00020513423056947279</v>
       </c>
       <c r="S27">
-        <v>-0.00020341667428457326</v>
+        <v>-7.0664859773725535e-005</v>
       </c>
       <c r="T27">
-        <v>-6.6733917280000789e-005</v>
+        <v>0.00012793728228741431</v>
       </c>
       <c r="U27">
-        <v>7.7305988355607012e-005</v>
+        <v>0.001967264050686892</v>
       </c>
       <c r="V27">
-        <v>0.0018935755013667404</v>
+        <v>0.0019142122248394489</v>
       </c>
       <c r="W27">
-        <v>0.0018334389485025486</v>
+        <v>0.0019834305206509056</v>
       </c>
       <c r="X27">
-        <v>0.0018891387148021982</v>
+        <v>0.0018988313543409519</v>
       </c>
       <c r="Y27">
-        <v>0.00183456994750856</v>
+        <v>0.0018822998102729143</v>
       </c>
       <c r="Z27">
-        <v>0.0018180984222387095</v>
+        <v>0.0022759411718895574</v>
       </c>
       <c r="AA27">
-        <v>0.0020639868662480367</v>
+        <v>0.0019415041072444105</v>
       </c>
       <c r="AB27">
-        <v>0.0029432384595682697</v>
+        <v>0.0033777615558874549</v>
       </c>
       <c r="AC27">
-        <v>0.001924335214845958</v>
+        <v>0.0020056866724088786</v>
       </c>
       <c r="AD27">
-        <v>0.0019111312802135357</v>
+        <v>0.0019660620714253133</v>
       </c>
       <c r="AE27">
-        <v>0.001863897426682916</v>
+        <v>0.0019763850615715046</v>
       </c>
       <c r="AF27">
-        <v>0.0018939931520485385</v>
+        <v>-7.9894829983063524e-005</v>
       </c>
       <c r="AG27">
-        <v>-6.7072254742328168e-005</v>
+        <v>-0.00016345267800116099</v>
       </c>
       <c r="AH27">
-        <v>-0.00025053007602249939</v>
+        <v>-6.1487889352208349e-005</v>
       </c>
       <c r="AI27">
-        <v>-0.00011841048449814581</v>
+        <v>0.0006327259074086879</v>
       </c>
       <c r="AJ27">
-        <v>0.00044394283598578403</v>
+        <v>0.0011801612215001655</v>
       </c>
       <c r="AK27">
-        <v>0.0014233412661106581</v>
+        <v>0.0018330580500524676</v>
       </c>
       <c r="AL27">
-        <v>0.0011481376518788465</v>
-      </c>
-      <c r="AM27">
-        <v>0.0010886179970883911</v>
+        <v>0.00080674880422724419</v>
       </c>
     </row>
     <row r="28">
@@ -3681,118 +3597,115 @@
         <v>41</v>
       </c>
       <c r="B28">
-        <v>0.086260314139312372</v>
+        <v>0.077412486000979178</v>
       </c>
       <c r="C28">
-        <v>0.00018028880580200262</v>
+        <v>0.00050489051232816039</v>
       </c>
       <c r="D28">
-        <v>0.00013941835798601202</v>
+        <v>0.00019472739121073547</v>
       </c>
       <c r="E28">
-        <v>-2.1330343543005354e-006</v>
+        <v>-2.9240620657251699e-006</v>
       </c>
       <c r="F28">
-        <v>4.2949284276583988e-006</v>
+        <v>4.6442823837224826e-006</v>
       </c>
       <c r="G28">
-        <v>-4.4167458056904373e-006</v>
+        <v>-7.5229560360237169e-006</v>
       </c>
       <c r="H28">
-        <v>1.7877426506447027e-005</v>
+        <v>7.732346975928806e-005</v>
       </c>
       <c r="I28">
-        <v>0.00019083186297889438</v>
+        <v>0.00021483790110557379</v>
       </c>
       <c r="J28">
-        <v>-0.00013206245752876963</v>
+        <v>-0.00029166135258044165</v>
       </c>
       <c r="K28">
-        <v>9.9822365165813014e-005</v>
+        <v>4.8351911503920545e-005</v>
       </c>
       <c r="L28">
-        <v>4.5260501006750799e-005</v>
+        <v>0.00025612766105230814</v>
       </c>
       <c r="M28">
-        <v>0.00015276095428486906</v>
+        <v>0.00021232101009288336</v>
       </c>
       <c r="N28">
-        <v>-7.1650648008393994e-005</v>
+        <v>-3.3623293024817613e-005</v>
       </c>
       <c r="O28">
-        <v>-9.6854730497470786e-005</v>
+        <v>-9.1021842269327114e-005</v>
       </c>
       <c r="P28">
-        <v>-6.7622387320927661e-005</v>
+        <v>-0.00011896915164282584</v>
       </c>
       <c r="Q28">
-        <v>0.00018307928558967512</v>
+        <v>-0.00010003898035512845</v>
       </c>
       <c r="R28">
-        <v>-4.2544086228771564e-005</v>
+        <v>0.0003284185756094835</v>
       </c>
       <c r="S28">
-        <v>-0.0001251591646184891</v>
+        <v>-0.00010260146132290903</v>
       </c>
       <c r="T28">
-        <v>-7.6464906383686901e-005</v>
+        <v>5.6903460382430712e-005</v>
       </c>
       <c r="U28">
-        <v>9.0900753679595635e-005</v>
+        <v>0.0019459654629032539</v>
       </c>
       <c r="V28">
-        <v>0.0019424186431544477</v>
+        <v>0.0018925716503594219</v>
       </c>
       <c r="W28">
-        <v>0.0018886555966209644</v>
+        <v>0.0019719113567190309</v>
       </c>
       <c r="X28">
-        <v>0.0019669755571359799</v>
+        <v>0.001896946618750383</v>
       </c>
       <c r="Y28">
-        <v>0.001879348419157829</v>
+        <v>0.0018685294126952552</v>
       </c>
       <c r="Z28">
-        <v>0.0018633938747233823</v>
+        <v>0.0021764611310518042</v>
       </c>
       <c r="AA28">
-        <v>0.0022475835433209586</v>
+        <v>0.0019284005631256468</v>
       </c>
       <c r="AB28">
-        <v>0.001924335214845958</v>
+        <v>0.0020056866724088786</v>
       </c>
       <c r="AC28">
-        <v>0.0034134851974582281</v>
+        <v>0.0041672777547806239</v>
       </c>
       <c r="AD28">
-        <v>0.001982080825665524</v>
+        <v>0.0019309088483252196</v>
       </c>
       <c r="AE28">
-        <v>0.0019477298534847194</v>
+        <v>0.0019658137050090905</v>
       </c>
       <c r="AF28">
-        <v>0.0019487811729004072</v>
+        <v>-0.00010926276719767014</v>
       </c>
       <c r="AG28">
-        <v>-8.5055588871036899e-005</v>
+        <v>-0.00025608749388359798</v>
       </c>
       <c r="AH28">
-        <v>-0.0001894041499082527</v>
+        <v>-0.00022270299430308732</v>
       </c>
       <c r="AI28">
-        <v>-3.0231762578789641e-005</v>
+        <v>0.00059088218376391504</v>
       </c>
       <c r="AJ28">
-        <v>0.00061247256305771891</v>
+        <v>0.0011478843812285839</v>
       </c>
       <c r="AK28">
-        <v>0.0011453366925330769</v>
+        <v>0.0014938340494617753</v>
       </c>
       <c r="AL28">
-        <v>0.0018104864785616903</v>
-      </c>
-      <c r="AM28">
-        <v>0.0016366025266154058</v>
+        <v>0.0026424958797788955</v>
       </c>
     </row>
     <row r="29">
@@ -3800,118 +3713,115 @@
         <v>42</v>
       </c>
       <c r="B29">
-        <v>0.072458950386281765</v>
+        <v>-0.0088653062691023254</v>
       </c>
       <c r="C29">
-        <v>0.000291846511250104</v>
+        <v>-0.00015306899027832898</v>
       </c>
       <c r="D29">
-        <v>0.00018063089442444053</v>
+        <v>0.00014295161164169952</v>
       </c>
       <c r="E29">
-        <v>-2.7023727237877694e-006</v>
+        <v>-2.3713942299986163e-006</v>
       </c>
       <c r="F29">
-        <v>4.4970639056239545e-006</v>
+        <v>-1.8014601718396664e-006</v>
       </c>
       <c r="G29">
-        <v>-7.318469928957008e-006</v>
+        <v>-5.2673926168255624e-006</v>
       </c>
       <c r="H29">
-        <v>5.4914822257967914e-005</v>
+        <v>-0.00075539575584244122</v>
       </c>
       <c r="I29">
-        <v>0.00024136483846119022</v>
+        <v>0.00071916467808292889</v>
       </c>
       <c r="J29">
-        <v>-0.00030052754175893684</v>
+        <v>0.0001929046550001304</v>
       </c>
       <c r="K29">
-        <v>4.5888264616702362e-005</v>
+        <v>-9.021305577256968e-005</v>
       </c>
       <c r="L29">
-        <v>0.00025299492889766331</v>
+        <v>-5.8992872018659383e-005</v>
       </c>
       <c r="M29">
-        <v>0.00020927702742451858</v>
+        <v>0.00019679202569056144</v>
       </c>
       <c r="N29">
-        <v>-2.8534753706098166e-005</v>
+        <v>-8.0590389062734462e-005</v>
       </c>
       <c r="O29">
-        <v>-8.2488468880938633e-005</v>
+        <v>-6.813341992730943e-005</v>
       </c>
       <c r="P29">
-        <v>-0.00011314137217187423</v>
+        <v>-0.00010895520225444251</v>
       </c>
       <c r="Q29">
-        <v>0.00013008402825159392</v>
+        <v>-0.00012657168058127788</v>
       </c>
       <c r="R29">
-        <v>-0.00022099665661149456</v>
+        <v>3.7555622515827747e-005</v>
       </c>
       <c r="S29">
-        <v>-0.00029691637225277238</v>
+        <v>-9.2692278011749811e-005</v>
       </c>
       <c r="T29">
-        <v>-9.9972528699135074e-005</v>
+        <v>0.00012808155560715189</v>
       </c>
       <c r="U29">
-        <v>6.016099059067304e-005</v>
+        <v>0.0019234477107744766</v>
       </c>
       <c r="V29">
-        <v>0.0019227344986453038</v>
+        <v>0.001859179841578501</v>
       </c>
       <c r="W29">
-        <v>0.0018698057176101293</v>
+        <v>0.0019119262111984207</v>
       </c>
       <c r="X29">
-        <v>0.0019515437354400192</v>
+        <v>0.0018376639034045792</v>
       </c>
       <c r="Y29">
-        <v>0.001869699950968591</v>
+        <v>0.001823432850529258</v>
       </c>
       <c r="Z29">
-        <v>0.0018522702834956363</v>
+        <v>0.0020787378323642199</v>
       </c>
       <c r="AA29">
-        <v>0.0021588279814631958</v>
+        <v>0.0018781895595058886</v>
       </c>
       <c r="AB29">
-        <v>0.0019111312802135357</v>
+        <v>0.0019660620714253133</v>
       </c>
       <c r="AC29">
-        <v>0.001982080825665524</v>
+        <v>0.0019309088483252196</v>
       </c>
       <c r="AD29">
-        <v>0.0041499303122968338</v>
+        <v>0.0039179172342092257</v>
       </c>
       <c r="AE29">
-        <v>0.0019173133716559037</v>
+        <v>0.0019301671011831536</v>
       </c>
       <c r="AF29">
-        <v>0.0019429230671101729</v>
+        <v>-9.2239920700476737e-005</v>
       </c>
       <c r="AG29">
-        <v>-0.00010724667970943642</v>
+        <v>-0.00026929332818242295</v>
       </c>
       <c r="AH29">
-        <v>-0.00025348161728336533</v>
+        <v>-8.476599841692866e-005</v>
       </c>
       <c r="AI29">
-        <v>-0.00021076159827140167</v>
+        <v>0.00056571544129724988</v>
       </c>
       <c r="AJ29">
-        <v>0.00057284658676428029</v>
+        <v>0.0012005659026965967</v>
       </c>
       <c r="AK29">
-        <v>0.0011365216748578252</v>
+        <v>0.0019804503616007449</v>
       </c>
       <c r="AL29">
-        <v>0.0014940945798894052</v>
-      </c>
-      <c r="AM29">
-        <v>0.0028848712914047916</v>
+        <v>0.0033377622952937749</v>
       </c>
     </row>
     <row r="30">
@@ -3919,118 +3829,115 @@
         <v>43</v>
       </c>
       <c r="B30">
-        <v>-0.010864260583592083</v>
+        <v>0.17022736059974367</v>
       </c>
       <c r="C30">
-        <v>-0.00033523854284169636</v>
+        <v>0.00027013316346486543</v>
       </c>
       <c r="D30">
-        <v>0.00013462608533284148</v>
+        <v>0.00014514729913945191</v>
       </c>
       <c r="E30">
-        <v>-2.2157275030365852e-006</v>
+        <v>-2.2500566971706337e-006</v>
       </c>
       <c r="F30">
-        <v>-1.8421644278118342e-006</v>
+        <v>1.4908629322377657e-006</v>
       </c>
       <c r="G30">
-        <v>-5.1417184329700977e-006</v>
+        <v>-3.6880853750586828e-006</v>
       </c>
       <c r="H30">
-        <v>-0.00076517547670724366</v>
+        <v>-0.00013285985941549426</v>
       </c>
       <c r="I30">
-        <v>0.00074796759064719802</v>
+        <v>7.7924201770455861e-005</v>
       </c>
       <c r="J30">
-        <v>0.000197154631043704</v>
+        <v>-0.00011321760410935953</v>
       </c>
       <c r="K30">
-        <v>-7.520566641779845e-005</v>
+        <v>0.00023199438151691497</v>
       </c>
       <c r="L30">
-        <v>-3.3782554708199455e-005</v>
+        <v>0.00013222417462586847</v>
       </c>
       <c r="M30">
-        <v>0.00023131173692410751</v>
+        <v>0.00020517669905663826</v>
       </c>
       <c r="N30">
-        <v>-5.3242901788881717e-005</v>
+        <v>6.8534125630500447e-005</v>
       </c>
       <c r="O30">
-        <v>-6.5754985739405636e-005</v>
+        <v>-0.00019539853167959694</v>
       </c>
       <c r="P30">
-        <v>-0.00010194100135895608</v>
+        <v>-6.2830049325270559e-005</v>
       </c>
       <c r="Q30">
-        <v>-0.0001409239923375646</v>
+        <v>-0.00023614508635891638</v>
       </c>
       <c r="R30">
-        <v>-0.00020154467741714279</v>
+        <v>8.748847568642356e-005</v>
       </c>
       <c r="S30">
-        <v>-0.00029953254315802347</v>
+        <v>-5.247179388989491e-005</v>
       </c>
       <c r="T30">
-        <v>-8.8852888139570726e-005</v>
+        <v>0.00016609261590552738</v>
       </c>
       <c r="U30">
-        <v>0.00013697508407044834</v>
+        <v>0.0019343044580812149</v>
       </c>
       <c r="V30">
-        <v>0.0019076429400642007</v>
+        <v>0.0018862661205086733</v>
       </c>
       <c r="W30">
-        <v>0.001841631944655864</v>
+        <v>0.0019247589717999031</v>
       </c>
       <c r="X30">
-        <v>0.0018976065159970572</v>
+        <v>0.0018871044816416663</v>
       </c>
       <c r="Y30">
-        <v>0.0018128962500671545</v>
+        <v>0.0018609015339981203</v>
       </c>
       <c r="Z30">
-        <v>0.0018079705445605881</v>
+        <v>0.0020937782408174512</v>
       </c>
       <c r="AA30">
-        <v>0.0020607525154057657</v>
+        <v>0.001916853063242227</v>
       </c>
       <c r="AB30">
-        <v>0.001863897426682916</v>
+        <v>0.0019763850615715046</v>
       </c>
       <c r="AC30">
-        <v>0.0019477298534847194</v>
+        <v>0.0019658137050090905</v>
       </c>
       <c r="AD30">
-        <v>0.0019173133716559037</v>
+        <v>0.0019301671011831536</v>
       </c>
       <c r="AE30">
-        <v>0.0039119170028607941</v>
+        <v>0.0039548406648221403</v>
       </c>
       <c r="AF30">
-        <v>0.0019112533679909692</v>
+        <v>-6.654747983272741e-005</v>
       </c>
       <c r="AG30">
-        <v>-8.9322729588173374e-005</v>
+        <v>-0.00010460881960008036</v>
       </c>
       <c r="AH30">
-        <v>-0.00026003020616816096</v>
+        <v>-0.00013420390396492055</v>
       </c>
       <c r="AI30">
-        <v>-7.2593454664606231e-005</v>
+        <v>0.00062292543724743192</v>
       </c>
       <c r="AJ30">
-        <v>0.00054880050246353639</v>
+        <v>0.0013163944594206949</v>
       </c>
       <c r="AK30">
-        <v>0.0011961987865550603</v>
+        <v>0.0011660896323616608</v>
       </c>
       <c r="AL30">
-        <v>0.0019920802527239635</v>
-      </c>
-      <c r="AM30">
-        <v>0.0033297305422530492</v>
+        <v>7.9155981832423981e-005</v>
       </c>
     </row>
     <row r="31">
@@ -4038,118 +3945,115 @@
         <v>44</v>
       </c>
       <c r="B31">
-        <v>0.16333390219557731</v>
+        <v>-0.01791512003178224</v>
       </c>
       <c r="C31">
-        <v>8.6968597651502708e-005</v>
+        <v>-7.8786167833850537e-005</v>
       </c>
       <c r="D31">
-        <v>0.00013649797022068436</v>
+        <v>-7.56302292125289e-006</v>
       </c>
       <c r="E31">
-        <v>-2.1004172589964419e-006</v>
+        <v>1.2049351089588824e-007</v>
       </c>
       <c r="F31">
-        <v>1.3523906111505447e-006</v>
+        <v>-5.7593407553714627e-007</v>
       </c>
       <c r="G31">
-        <v>-3.5026009717748754e-006</v>
+        <v>1.4605478834024842e-006</v>
       </c>
       <c r="H31">
-        <v>-0.00014617153448102309</v>
+        <v>2.6982426093706637e-005</v>
       </c>
       <c r="I31">
-        <v>0.00010320281194527723</v>
+        <v>-2.4816777708662356e-005</v>
       </c>
       <c r="J31">
-        <v>-0.00010957095615421876</v>
+        <v>8.0922425879660377e-005</v>
       </c>
       <c r="K31">
-        <v>0.00023394760552095681</v>
+        <v>-3.649893703404745e-005</v>
       </c>
       <c r="L31">
-        <v>0.00014582347394210843</v>
+        <v>-5.0776866518007389e-005</v>
       </c>
       <c r="M31">
-        <v>0.0002207292658957643</v>
+        <v>-4.9021864001511941e-005</v>
       </c>
       <c r="N31">
-        <v>9.1980433528481096e-005</v>
+        <v>4.5884060363310199e-006</v>
       </c>
       <c r="O31">
-        <v>-0.00018327013574199926</v>
+        <v>1.7860125300843399e-005</v>
       </c>
       <c r="P31">
-        <v>-6.6273774619723515e-005</v>
+        <v>2.6914162160587055e-005</v>
       </c>
       <c r="Q31">
-        <v>-0.00010696561359864291</v>
+        <v>5.9550340722653824e-005</v>
       </c>
       <c r="R31">
-        <v>-0.00020517319066285476</v>
+        <v>-3.1293185513626155e-005</v>
       </c>
       <c r="S31">
-        <v>-0.00040533842495678058</v>
+        <v>0.00014427981051894279</v>
       </c>
       <c r="T31">
-        <v>-4.9276418980819664e-005</v>
+        <v>-1.069406068963177e-005</v>
       </c>
       <c r="U31">
-        <v>0.00017068610340153188</v>
+        <v>-6.9094747112181216e-005</v>
       </c>
       <c r="V31">
-        <v>0.0019090565111093919</v>
+        <v>-8.1414709880193694e-005</v>
       </c>
       <c r="W31">
-        <v>0.0018622309679966918</v>
+        <v>-7.3788602868653645e-005</v>
       </c>
       <c r="X31">
-        <v>0.0019019571104856216</v>
+        <v>-6.0230969855493805e-005</v>
       </c>
       <c r="Y31">
-        <v>0.001851837600131973</v>
+        <v>-5.8479465151153238e-005</v>
       </c>
       <c r="Z31">
-        <v>0.0018376257676263566</v>
+        <v>-0.00014408431904570646</v>
       </c>
       <c r="AA31">
-        <v>0.002067077575224595</v>
+        <v>-7.1064037082577212e-005</v>
       </c>
       <c r="AB31">
-        <v>0.0018939931520485385</v>
+        <v>-7.9894829983063524e-005</v>
       </c>
       <c r="AC31">
-        <v>0.0019487811729004072</v>
+        <v>-0.00010926276719767014</v>
       </c>
       <c r="AD31">
-        <v>0.0019429230671101729</v>
+        <v>-9.2239920700476737e-005</v>
       </c>
       <c r="AE31">
-        <v>0.0019112533679909692</v>
+        <v>-6.654747983272741e-005</v>
       </c>
       <c r="AF31">
-        <v>0.0039577131522792039</v>
+        <v>0.00017232197405195435</v>
       </c>
       <c r="AG31">
-        <v>-6.3602728840293774e-005</v>
+        <v>0.00018954699612717604</v>
       </c>
       <c r="AH31">
-        <v>-0.00010264885535290883</v>
+        <v>-8.2502075848269428e-005</v>
       </c>
       <c r="AI31">
-        <v>-0.00012214253404733809</v>
+        <v>-1.8472011656115589e-005</v>
       </c>
       <c r="AJ31">
-        <v>0.00060337995889458626</v>
+        <v>-3.8992729582474142e-005</v>
       </c>
       <c r="AK31">
-        <v>0.0012952848893046092</v>
+        <v>-0.00025180507306524907</v>
       </c>
       <c r="AL31">
-        <v>0.0011491266536023058</v>
-      </c>
-      <c r="AM31">
-        <v>0.00015253190447202074</v>
+        <v>-0.011160671010331719</v>
       </c>
     </row>
     <row r="32">
@@ -4157,118 +4061,115 @@
         <v>45</v>
       </c>
       <c r="B32">
-        <v>-0.01718908587978164</v>
+        <v>0.016003367649744461</v>
       </c>
       <c r="C32">
-        <v>-9.6348997729901173e-005</v>
+        <v>-0.00057531693783287492</v>
       </c>
       <c r="D32">
-        <v>-8.911273599796461e-006</v>
+        <v>-2.6537146479572483e-005</v>
       </c>
       <c r="E32">
-        <v>1.4246537473365746e-007</v>
+        <v>4.0155626947451227e-007</v>
       </c>
       <c r="F32">
-        <v>-7.0758071077323385e-007</v>
+        <v>-3.7426835891981924e-006</v>
       </c>
       <c r="G32">
-        <v>1.5367247133585213e-006</v>
+        <v>6.2259686470278653e-006</v>
       </c>
       <c r="H32">
-        <v>2.0891420905773262e-005</v>
+        <v>-1.6929237222918203e-005</v>
       </c>
       <c r="I32">
-        <v>-2.4316231834377449e-005</v>
+        <v>-0.00032987204953516995</v>
       </c>
       <c r="J32">
-        <v>8.1711130071494554e-005</v>
+        <v>0.00061298317654607604</v>
       </c>
       <c r="K32">
-        <v>-3.2849143929438887e-005</v>
+        <v>-1.8475101305817144e-005</v>
       </c>
       <c r="L32">
-        <v>-4.2051431883492871e-005</v>
+        <v>-0.00013007171642184659</v>
       </c>
       <c r="M32">
-        <v>-3.7547916502796498e-005</v>
+        <v>-0.00034537691236294701</v>
       </c>
       <c r="N32">
-        <v>1.2948083191670457e-005</v>
+        <v>-9.8140343837553731e-005</v>
       </c>
       <c r="O32">
-        <v>1.2654912550386738e-005</v>
+        <v>-5.1172471083111583e-005</v>
       </c>
       <c r="P32">
-        <v>3.0839067638836617e-005</v>
+        <v>7.3090305524119533e-005</v>
       </c>
       <c r="Q32">
-        <v>-5.7755553879237998e-005</v>
+        <v>4.123373150175983e-005</v>
       </c>
       <c r="R32">
-        <v>-2.3421865775083859e-005</v>
+        <v>-0.00016126023072227601</v>
       </c>
       <c r="S32">
-        <v>3.9084820280812236e-005</v>
+        <v>0.00023991112119895949</v>
       </c>
       <c r="T32">
-        <v>0.00014613747172832964</v>
+        <v>4.1218898197605686e-006</v>
       </c>
       <c r="U32">
-        <v>-3.6427000747347316e-006</v>
+        <v>-2.800541060387512e-005</v>
       </c>
       <c r="V32">
-        <v>-6.1797978299392184e-005</v>
+        <v>-0.00015782093667063616</v>
       </c>
       <c r="W32">
-        <v>-8.0056414420442713e-005</v>
+        <v>-0.00014837569300896051</v>
       </c>
       <c r="X32">
-        <v>-7.348242209479969e-005</v>
+        <v>-1.4933057935808671e-005</v>
       </c>
       <c r="Y32">
-        <v>-6.1542679526740732e-005</v>
+        <v>2.2584090247459543e-005</v>
       </c>
       <c r="Z32">
-        <v>-5.7049321145558635e-005</v>
+        <v>-0.00073929879812733115</v>
       </c>
       <c r="AA32">
-        <v>-0.000140504742674733</v>
+        <v>-0.00025048121641180329</v>
       </c>
       <c r="AB32">
-        <v>-6.7072254742328168e-005</v>
+        <v>-0.00016345267800116099</v>
       </c>
       <c r="AC32">
-        <v>-8.5055588871036899e-005</v>
+        <v>-0.00025608749388359798</v>
       </c>
       <c r="AD32">
-        <v>-0.00010724667970943642</v>
+        <v>-0.00026929332818242295</v>
       </c>
       <c r="AE32">
-        <v>-8.9322729588173374e-005</v>
+        <v>-0.00010460881960008036</v>
       </c>
       <c r="AF32">
-        <v>-6.3602728840293774e-005</v>
+        <v>0.00018954699612717604</v>
       </c>
       <c r="AG32">
-        <v>0.00017438679587395534</v>
+        <v>0.0033561998532487015</v>
       </c>
       <c r="AH32">
-        <v>0.00019334802237021276</v>
+        <v>0.00064166493794026204</v>
       </c>
       <c r="AI32">
-        <v>-8.2466841731568784e-005</v>
+        <v>4.0244340169116009e-005</v>
       </c>
       <c r="AJ32">
-        <v>-1.6120393791763631e-005</v>
+        <v>-2.4277971773841583e-005</v>
       </c>
       <c r="AK32">
-        <v>-3.797094424627754e-005</v>
+        <v>-0.0016560235428408898</v>
       </c>
       <c r="AL32">
-        <v>-0.00025736969335646981</v>
-      </c>
-      <c r="AM32">
-        <v>-0.011262860929551824</v>
+        <v>-0.01664202325557082</v>
       </c>
     </row>
     <row r="33">
@@ -4276,118 +4177,115 @@
         <v>46</v>
       </c>
       <c r="B33">
-        <v>0.001327881184615329</v>
+        <v>0.051664386645568244</v>
       </c>
       <c r="C33">
-        <v>-0.00056375718196254726</v>
+        <v>-0.00029971967865791236</v>
       </c>
       <c r="D33">
-        <v>-3.5243251367064223e-005</v>
+        <v>-5.5018858766613804e-005</v>
       </c>
       <c r="E33">
-        <v>5.406441439428816e-007</v>
+        <v>8.6914154417948184e-007</v>
       </c>
       <c r="F33">
-        <v>-3.3773874322428818e-006</v>
+        <v>1.0272851738511629e-006</v>
       </c>
       <c r="G33">
-        <v>6.5949326141458778e-006</v>
+        <v>7.7950723154255991e-006</v>
       </c>
       <c r="H33">
-        <v>-3.3210052751427618e-005</v>
+        <v>0.000149165522473258</v>
       </c>
       <c r="I33">
-        <v>-0.00031736160748354215</v>
+        <v>-0.00044900559712765325</v>
       </c>
       <c r="J33">
-        <v>0.00062194645657981688</v>
+        <v>0.00019641808547011733</v>
       </c>
       <c r="K33">
-        <v>6.3573291048267446e-006</v>
+        <v>6.1964233863514889e-005</v>
       </c>
       <c r="L33">
-        <v>-8.835946198237671e-005</v>
+        <v>-9.7687323686359239e-005</v>
       </c>
       <c r="M33">
-        <v>-0.00027870482722584886</v>
+        <v>-0.00031356053569504263</v>
       </c>
       <c r="N33">
-        <v>-4.8467231561043298e-005</v>
+        <v>-0.00018765639706114538</v>
       </c>
       <c r="O33">
-        <v>-6.4173155977544083e-005</v>
+        <v>-2.2621205408135446e-005</v>
       </c>
       <c r="P33">
-        <v>9.7030238788692417e-005</v>
+        <v>6.7007874260891387e-005</v>
       </c>
       <c r="Q33">
-        <v>-0.00017758135928915963</v>
+        <v>-4.5066907372377584e-005</v>
       </c>
       <c r="R33">
-        <v>-7.1412653764946557e-006</v>
+        <v>-0.00014607868310096154</v>
       </c>
       <c r="S33">
-        <v>7.065540882063813e-005</v>
+        <v>3.0318174977662232e-006</v>
       </c>
       <c r="T33">
-        <v>0.0002423547939751497</v>
+        <v>-8.0479016927479654e-005</v>
       </c>
       <c r="U33">
-        <v>2.080913430079585e-005</v>
+        <v>0.00020423697293106579</v>
       </c>
       <c r="V33">
-        <v>-2.446560032781501e-005</v>
+        <v>1.328343357181967e-005</v>
       </c>
       <c r="W33">
-        <v>-0.00016046336404121266</v>
+        <v>-0.00014209814536660597</v>
       </c>
       <c r="X33">
-        <v>-0.00014909826210742546</v>
+        <v>5.1566806203337068e-005</v>
       </c>
       <c r="Y33">
-        <v>-6.1583855512882578e-005</v>
+        <v>-7.8491701891405814e-005</v>
       </c>
       <c r="Z33">
-        <v>2.2803861424251976e-005</v>
+        <v>-0.00063263093883486013</v>
       </c>
       <c r="AA33">
-        <v>-0.00070927881202781492</v>
+        <v>-0.00011899993288583591</v>
       </c>
       <c r="AB33">
-        <v>-0.00025053007602249939</v>
+        <v>-6.1487889352208349e-005</v>
       </c>
       <c r="AC33">
-        <v>-0.0001894041499082527</v>
+        <v>-0.00022270299430308732</v>
       </c>
       <c r="AD33">
-        <v>-0.00025348161728336533</v>
+        <v>-8.476599841692866e-005</v>
       </c>
       <c r="AE33">
-        <v>-0.00026003020616816096</v>
+        <v>-0.00013420390396492055</v>
       </c>
       <c r="AF33">
-        <v>-0.00010264885535290883</v>
+        <v>-8.2502075848269428e-005</v>
       </c>
       <c r="AG33">
-        <v>0.00019334802237021276</v>
+        <v>0.00064166493794026204</v>
       </c>
       <c r="AH33">
-        <v>0.0033614801655945095</v>
+        <v>0.0035920861098678565</v>
       </c>
       <c r="AI33">
-        <v>0.00063620335548190791</v>
+        <v>5.31287541783226e-005</v>
       </c>
       <c r="AJ33">
-        <v>4.7678304777290861e-005</v>
+        <v>-4.7440904431339873e-006</v>
       </c>
       <c r="AK33">
-        <v>-3.1815735959973661e-005</v>
+        <v>-0.0016256576694089822</v>
       </c>
       <c r="AL33">
-        <v>-0.0016033092197683119</v>
-      </c>
-      <c r="AM33">
-        <v>-0.016784359895925673</v>
+        <v>0.0017974060955813012</v>
       </c>
     </row>
     <row r="34">
@@ -4395,118 +4293,115 @@
         <v>47</v>
       </c>
       <c r="B34">
-        <v>0.04219971972802089</v>
+        <v>-0.088911268083306141</v>
       </c>
       <c r="C34">
-        <v>-0.00018499049563647837</v>
+        <v>-5.652680391550393e-005</v>
       </c>
       <c r="D34">
-        <v>-8.2021987414312037e-005</v>
+        <v>5.1065744378084657e-006</v>
       </c>
       <c r="E34">
-        <v>1.2577644629238564e-006</v>
+        <v>-1.3338421361012596e-007</v>
       </c>
       <c r="F34">
-        <v>1.2229827263314052e-006</v>
+        <v>1.5691615755791336e-006</v>
       </c>
       <c r="G34">
-        <v>7.8741596823225976e-006</v>
+        <v>-6.773704474306016e-007</v>
       </c>
       <c r="H34">
-        <v>0.00011757775743287304</v>
+        <v>-7.896401514970858e-005</v>
       </c>
       <c r="I34">
-        <v>-0.00041173802828243654</v>
+        <v>7.0945308717769223e-005</v>
       </c>
       <c r="J34">
-        <v>0.0002014568059194909</v>
+        <v>-0.00026688485360133187</v>
       </c>
       <c r="K34">
-        <v>8.8196267273086171e-005</v>
+        <v>-0.00017988181928324374</v>
       </c>
       <c r="L34">
-        <v>-3.0498484198491637e-005</v>
+        <v>-0.00017376644155001606</v>
       </c>
       <c r="M34">
-        <v>-0.00025642724126674079</v>
+        <v>-7.2145239984655433e-005</v>
       </c>
       <c r="N34">
-        <v>-0.0001256434594235226</v>
+        <v>-0.00015072067519570492</v>
       </c>
       <c r="O34">
-        <v>-2.4310245680168852e-005</v>
+        <v>-0.00011815262586697151</v>
       </c>
       <c r="P34">
-        <v>7.2168682090197723e-005</v>
+        <v>8.2514014695242639e-005</v>
       </c>
       <c r="Q34">
-        <v>7.9531004010830603e-006</v>
+        <v>-0.00019753055342053782</v>
       </c>
       <c r="R34">
-        <v>0.00016203259298294779</v>
+        <v>-8.2136315290901583e-005</v>
       </c>
       <c r="S34">
-        <v>0.00014888319302826594</v>
+        <v>-1.3490536425988381e-005</v>
       </c>
       <c r="T34">
-        <v>2.5788455762674675e-006</v>
+        <v>-0.00012194659644551445</v>
       </c>
       <c r="U34">
-        <v>-8.9286662794248574e-005</v>
+        <v>0.00059224413869626673</v>
       </c>
       <c r="V34">
-        <v>0.00019412403023791542</v>
+        <v>0.00048585264649225334</v>
       </c>
       <c r="W34">
-        <v>1.4623108289534632e-005</v>
+        <v>0.00062447968276697083</v>
       </c>
       <c r="X34">
-        <v>-0.00012723979908432255</v>
+        <v>0.00048792132441952948</v>
       </c>
       <c r="Y34">
-        <v>1.5587797207983179e-006</v>
+        <v>0.00039237678988009872</v>
       </c>
       <c r="Z34">
-        <v>-7.8248246057880831e-005</v>
+        <v>0.00054771532522141344</v>
       </c>
       <c r="AA34">
-        <v>-0.00060994808775402499</v>
+        <v>0.0004622755930847283</v>
       </c>
       <c r="AB34">
-        <v>-0.00011841048449814581</v>
+        <v>0.0006327259074086879</v>
       </c>
       <c r="AC34">
-        <v>-3.0231762578789641e-005</v>
+        <v>0.00059088218376391504</v>
       </c>
       <c r="AD34">
-        <v>-0.00021076159827140167</v>
+        <v>0.00056571544129724988</v>
       </c>
       <c r="AE34">
-        <v>-7.2593454664606231e-005</v>
+        <v>0.00062292543724743192</v>
       </c>
       <c r="AF34">
-        <v>-0.00012214253404733809</v>
+        <v>-1.8472011656115589e-005</v>
       </c>
       <c r="AG34">
-        <v>-8.2466841731568784e-005</v>
+        <v>4.0244340169116009e-005</v>
       </c>
       <c r="AH34">
-        <v>0.00063620335548190791</v>
+        <v>5.31287541783226e-005</v>
       </c>
       <c r="AI34">
-        <v>0.0035649673453169864</v>
+        <v>0.0020075329663204783</v>
       </c>
       <c r="AJ34">
-        <v>6.1708524516597418e-005</v>
+        <v>0.00047197478083274574</v>
       </c>
       <c r="AK34">
-        <v>1.208474698705499e-005</v>
+        <v>0.00065414291159683526</v>
       </c>
       <c r="AL34">
-        <v>-0.001596556818827595</v>
-      </c>
-      <c r="AM34">
-        <v>0.0020466029037080891</v>
+        <v>0.00063257041925911424</v>
       </c>
     </row>
     <row r="35">
@@ -4514,118 +4409,115 @@
         <v>48</v>
       </c>
       <c r="B35">
-        <v>-0.092824400062525611</v>
+        <v>0.2404544031560685</v>
       </c>
       <c r="C35">
-        <v>0.00012267086646320507</v>
+        <v>-0.00058324750785453952</v>
       </c>
       <c r="D35">
-        <v>-1.4458036443547144e-005</v>
+        <v>1.8028906569158079e-005</v>
       </c>
       <c r="E35">
-        <v>1.5938710802661287e-007</v>
+        <v>-5.2044630711463286e-007</v>
       </c>
       <c r="F35">
-        <v>1.4643168722367507e-006</v>
+        <v>1.5085316360954403e-006</v>
       </c>
       <c r="G35">
-        <v>-5.1269022852124618e-007</v>
+        <v>1.1410059634496249e-006</v>
       </c>
       <c r="H35">
-        <v>-7.841393178064694e-005</v>
+        <v>-0.00031903731942996576</v>
       </c>
       <c r="I35">
-        <v>6.4445621554079686e-005</v>
+        <v>-0.00024893662899198551</v>
       </c>
       <c r="J35">
-        <v>-0.00028472211757559477</v>
+        <v>0.00050394462782265409</v>
       </c>
       <c r="K35">
-        <v>-0.0001838264104221798</v>
+        <v>0.00018855087991724335</v>
       </c>
       <c r="L35">
-        <v>-0.00018331029926357313</v>
+        <v>5.2640332745617529e-005</v>
       </c>
       <c r="M35">
-        <v>-8.7804087075625764e-005</v>
+        <v>0.00011089309233427985</v>
       </c>
       <c r="N35">
-        <v>-0.00015933562142264428</v>
+        <v>-6.1731432260778369e-005</v>
       </c>
       <c r="O35">
-        <v>-0.00010962948838037818</v>
+        <v>-0.0002008529690260274</v>
       </c>
       <c r="P35">
-        <v>8.1472330471192615e-005</v>
+        <v>3.3927801326661394e-005</v>
       </c>
       <c r="Q35">
-        <v>0.00014254298045978482</v>
+        <v>-0.0001673118952549356</v>
       </c>
       <c r="R35">
-        <v>0.00021026214061750648</v>
+        <v>5.6853497491108306e-005</v>
       </c>
       <c r="S35">
-        <v>2.6178915629178779e-005</v>
+        <v>-4.166738257455364e-005</v>
       </c>
       <c r="T35">
-        <v>-1.087782945173978e-005</v>
+        <v>5.6130485394423487e-005</v>
       </c>
       <c r="U35">
-        <v>-0.00014094445270912111</v>
+        <v>0.0012144513629366524</v>
       </c>
       <c r="V35">
-        <v>0.0005724794586272103</v>
+        <v>0.0010697430335632014</v>
       </c>
       <c r="W35">
-        <v>0.00046588155042047853</v>
+        <v>0.0011006478529723179</v>
       </c>
       <c r="X35">
-        <v>0.00060729061207093335</v>
+        <v>0.0010984911221362502</v>
       </c>
       <c r="Y35">
-        <v>0.00044944452169753111</v>
+        <v>0.0010532951890321633</v>
       </c>
       <c r="Z35">
-        <v>0.00037506279914277074</v>
+        <v>0.00080382141040420099</v>
       </c>
       <c r="AA35">
-        <v>0.00052747675100903104</v>
+        <v>0.0014471396875052151</v>
       </c>
       <c r="AB35">
-        <v>0.00044394283598578403</v>
+        <v>0.0011801612215001655</v>
       </c>
       <c r="AC35">
-        <v>0.00061247256305771891</v>
+        <v>0.0011478843812285839</v>
       </c>
       <c r="AD35">
-        <v>0.00057284658676428029</v>
+        <v>0.0012005659026965967</v>
       </c>
       <c r="AE35">
-        <v>0.00054880050246353639</v>
+        <v>0.0013163944594206949</v>
       </c>
       <c r="AF35">
-        <v>0.00060337995889458626</v>
+        <v>-3.8992729582474142e-005</v>
       </c>
       <c r="AG35">
-        <v>-1.6120393791763631e-005</v>
+        <v>-2.4277971773841583e-005</v>
       </c>
       <c r="AH35">
-        <v>4.7678304777290861e-005</v>
+        <v>-4.7440904431339873e-006</v>
       </c>
       <c r="AI35">
-        <v>6.1708524516597418e-005</v>
+        <v>0.00047197478083274574</v>
       </c>
       <c r="AJ35">
-        <v>0.0020283829366105361</v>
+        <v>0.0061020127740239937</v>
       </c>
       <c r="AK35">
-        <v>0.00046388824511721139</v>
+        <v>0.0001220315591753604</v>
       </c>
       <c r="AL35">
-        <v>0.00064659452488820962</v>
-      </c>
-      <c r="AM35">
-        <v>0.00056406037807665149</v>
+        <v>0.0019590016785516751</v>
       </c>
     </row>
     <row r="36">
@@ -4633,118 +4525,115 @@
         <v>49</v>
       </c>
       <c r="B36">
-        <v>0.22221596647065078</v>
+        <v>0.028876497907552125</v>
       </c>
       <c r="C36">
-        <v>-0.00049944234047465293</v>
+        <v>0.0012766839756755237</v>
       </c>
       <c r="D36">
-        <v>-1.7499261623238078e-006</v>
+        <v>0.0002865514005017597</v>
       </c>
       <c r="E36">
-        <v>-2.1929725955146596e-007</v>
+        <v>-4.6057223438055665e-006</v>
       </c>
       <c r="F36">
-        <v>1.3734581828507825e-006</v>
+        <v>1.7675754068946156e-005</v>
       </c>
       <c r="G36">
-        <v>1.3234515750249751e-006</v>
+        <v>-3.0767736225818495e-005</v>
       </c>
       <c r="H36">
-        <v>-0.00032331174718122424</v>
+        <v>0.00038975016598094461</v>
       </c>
       <c r="I36">
-        <v>-0.00023658805361457787</v>
+        <v>0.0017561149839221031</v>
       </c>
       <c r="J36">
-        <v>0.00053385650180145182</v>
+        <v>-0.0017520966706413526</v>
       </c>
       <c r="K36">
-        <v>0.00019831270147734574</v>
+        <v>0.00043575863269854596</v>
       </c>
       <c r="L36">
-        <v>7.6012699823187061e-005</v>
+        <v>0.001052518297543212</v>
       </c>
       <c r="M36">
-        <v>0.0001241885259186776</v>
+        <v>0.003083552768238876</v>
       </c>
       <c r="N36">
-        <v>-5.3180075123619025e-005</v>
+        <v>0.0007289240914948817</v>
       </c>
       <c r="O36">
-        <v>-0.00020011437162407896</v>
+        <v>-3.8619813065707796e-005</v>
       </c>
       <c r="P36">
-        <v>4.9074531602562288e-005</v>
+        <v>-0.0001540537768883164</v>
       </c>
       <c r="Q36">
-        <v>0.0001895556842561616</v>
+        <v>0.00040364711340727449</v>
       </c>
       <c r="R36">
-        <v>0.00010601426602502208</v>
+        <v>0.0012600189609595931</v>
       </c>
       <c r="S36">
-        <v>-3.1948945107821824e-005</v>
+        <v>-0.00036338975652421696</v>
       </c>
       <c r="T36">
-        <v>-4.0352825567972067e-005</v>
+        <v>0.00014620496653568356</v>
       </c>
       <c r="U36">
-        <v>4.8919972715290717e-005</v>
+        <v>0.0018557043096712076</v>
       </c>
       <c r="V36">
-        <v>0.0011834377782937802</v>
+        <v>0.0013332469138491758</v>
       </c>
       <c r="W36">
-        <v>0.0010531376170443262</v>
+        <v>0.0018522942790446585</v>
       </c>
       <c r="X36">
-        <v>0.0010822235155489822</v>
+        <v>0.0010068176402697609</v>
       </c>
       <c r="Y36">
-        <v>0.0010410031428158138</v>
+        <v>0.0012138140024918758</v>
       </c>
       <c r="Z36">
-        <v>0.0010315650564605198</v>
+        <v>0.0053073350236214987</v>
       </c>
       <c r="AA36">
-        <v>0.00080031374260806421</v>
+        <v>0.0011588471591380423</v>
       </c>
       <c r="AB36">
-        <v>0.0014233412661106581</v>
+        <v>0.0018330580500524676</v>
       </c>
       <c r="AC36">
-        <v>0.0011453366925330769</v>
+        <v>0.0014938340494617753</v>
       </c>
       <c r="AD36">
-        <v>0.0011365216748578252</v>
+        <v>0.0019804503616007449</v>
       </c>
       <c r="AE36">
-        <v>0.0011961987865550603</v>
+        <v>0.0011660896323616608</v>
       </c>
       <c r="AF36">
-        <v>0.0012952848893046092</v>
+        <v>-0.00025180507306524907</v>
       </c>
       <c r="AG36">
-        <v>-3.797094424627754e-005</v>
+        <v>-0.0016560235428408898</v>
       </c>
       <c r="AH36">
-        <v>-3.1815735959973661e-005</v>
+        <v>-0.0016256576694089822</v>
       </c>
       <c r="AI36">
-        <v>1.208474698705499e-005</v>
+        <v>0.00065414291159683526</v>
       </c>
       <c r="AJ36">
-        <v>0.00046388824511721139</v>
+        <v>0.0001220315591753604</v>
       </c>
       <c r="AK36">
-        <v>0.0062194059551536141</v>
+        <v>0.019679599472966124</v>
       </c>
       <c r="AL36">
-        <v>0.00016039434828146563</v>
-      </c>
-      <c r="AM36">
-        <v>0.0020623072868582969</v>
+        <v>0.017623683104807324</v>
       </c>
     </row>
     <row r="37">
@@ -4752,237 +4641,115 @@
         <v>50</v>
       </c>
       <c r="B37">
-        <v>0.013834836100327983</v>
+        <v>-5.2549662451763979</v>
       </c>
       <c r="C37">
-        <v>0.0012776473812648043</v>
+        <v>0.0051150678178404213</v>
       </c>
       <c r="D37">
-        <v>0.00025715286964574438</v>
+        <v>-0.0041887917459276849</v>
       </c>
       <c r="E37">
-        <v>-4.1672804853540345e-006</v>
+        <v>6.0416784282312744e-005</v>
       </c>
       <c r="F37">
-        <v>1.7868796407769091e-005</v>
+        <v>-5.8295662480047636e-005</v>
       </c>
       <c r="G37">
-        <v>-3.1001578646098902e-005</v>
+        <v>-0.00019155574543252437</v>
       </c>
       <c r="H37">
-        <v>0.00035913374482540511</v>
+        <v>-0.0049979091070046656</v>
       </c>
       <c r="I37">
-        <v>0.001702080966160811</v>
+        <v>0.0026945097980674293</v>
       </c>
       <c r="J37">
-        <v>-0.0017438329997150647</v>
+        <v>-0.012132987121470247</v>
       </c>
       <c r="K37">
-        <v>0.00041130176588057531</v>
+        <v>0.001181021398127916</v>
       </c>
       <c r="L37">
-        <v>0.00095399970196039571</v>
+        <v>0.0028666716242164037</v>
       </c>
       <c r="M37">
-        <v>0.0028899975583858394</v>
+        <v>0.0040992740004984918</v>
       </c>
       <c r="N37">
-        <v>0.00052096746028740867</v>
+        <v>0.00090945056340335784</v>
       </c>
       <c r="O37">
-        <v>-5.5309452233983248e-005</v>
+        <v>4.3470608544697587e-005</v>
       </c>
       <c r="P37">
-        <v>-0.00013130917894927551</v>
+        <v>-0.00094907875100946014</v>
       </c>
       <c r="Q37">
-        <v>0.0015058865887626512</v>
+        <v>-0.0032877227298290321</v>
       </c>
       <c r="R37">
-        <v>9.6809391473596379e-005</v>
+        <v>0.0020326671694665009</v>
       </c>
       <c r="S37">
-        <v>0.00044073173008572428</v>
+        <v>-0.0099010743776852192</v>
       </c>
       <c r="T37">
-        <v>-0.00036242969867932018</v>
+        <v>-0.00097122339958913631</v>
       </c>
       <c r="U37">
-        <v>7.3086596568319034e-005</v>
+        <v>0.0015986915576964179</v>
       </c>
       <c r="V37">
-        <v>0.001832102022181187</v>
+        <v>0.0020554803050226098</v>
       </c>
       <c r="W37">
-        <v>0.0013275134412555449</v>
+        <v>0.00083708268416976626</v>
       </c>
       <c r="X37">
-        <v>0.001833581487856372</v>
+        <v>-0.00035028013161433023</v>
       </c>
       <c r="Y37">
-        <v>0.00092339645879814872</v>
+        <v>-0.00083420667951310907</v>
       </c>
       <c r="Z37">
-        <v>0.0012200845725457501</v>
+        <v>0.0062611633868852228</v>
       </c>
       <c r="AA37">
-        <v>0.0052641329408566855</v>
+        <v>0.0011646950095624917</v>
       </c>
       <c r="AB37">
-        <v>0.0011481376518788465</v>
+        <v>0.00080674880422724419</v>
       </c>
       <c r="AC37">
-        <v>0.0018104864785616903</v>
+        <v>0.0026424958797788955</v>
       </c>
       <c r="AD37">
-        <v>0.0014940945798894052</v>
+        <v>0.0033377622952937749</v>
       </c>
       <c r="AE37">
-        <v>0.0019920802527239635</v>
+        <v>7.9155981832423981e-005</v>
       </c>
       <c r="AF37">
-        <v>0.0011491266536023058</v>
+        <v>-0.011160671010331719</v>
       </c>
       <c r="AG37">
-        <v>-0.00025736969335646981</v>
+        <v>-0.01664202325557082</v>
       </c>
       <c r="AH37">
-        <v>-0.0016033092197683119</v>
+        <v>0.0017974060955813012</v>
       </c>
       <c r="AI37">
-        <v>-0.001596556818827595</v>
+        <v>0.00063257041925911424</v>
       </c>
       <c r="AJ37">
-        <v>0.00064659452488820962</v>
+        <v>0.0019590016785516751</v>
       </c>
       <c r="AK37">
-        <v>0.00016039434828146563</v>
+        <v>0.017623683104807324</v>
       </c>
       <c r="AL37">
-        <v>0.019911388137815005</v>
-      </c>
-      <c r="AM37">
-        <v>0.018174698798309546</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38">
-        <v>-5.3722676437175929</v>
-      </c>
-      <c r="C38">
-        <v>0.0016507039351127129</v>
-      </c>
-      <c r="D38">
-        <v>-0.0041141183581086017</v>
-      </c>
-      <c r="E38">
-        <v>5.9039867462360558e-005</v>
-      </c>
-      <c r="F38">
-        <v>-4.974261260235033e-005</v>
-      </c>
-      <c r="G38">
-        <v>-0.00020024178315272156</v>
-      </c>
-      <c r="H38">
-        <v>-0.0048025385726116337</v>
-      </c>
-      <c r="I38">
-        <v>0.0028352063710509329</v>
-      </c>
-      <c r="J38">
-        <v>-0.011405369249832899</v>
-      </c>
-      <c r="K38">
-        <v>0.0010883399077574315</v>
-      </c>
-      <c r="L38">
-        <v>0.0026324239523177273</v>
-      </c>
-      <c r="M38">
-        <v>0.0034055267868486018</v>
-      </c>
-      <c r="N38">
-        <v>0.00048887595754341408</v>
-      </c>
-      <c r="O38">
-        <v>0.00039824274032360715</v>
-      </c>
-      <c r="P38">
-        <v>-0.0012331357582365326</v>
-      </c>
-      <c r="Q38">
-        <v>0.00017465309214422658</v>
-      </c>
-      <c r="R38">
-        <v>-0.0024304330040109401</v>
-      </c>
-      <c r="S38">
-        <v>-0.0058380059149684693</v>
-      </c>
-      <c r="T38">
-        <v>-0.0099769069322157497</v>
-      </c>
-      <c r="U38">
-        <v>-0.0014223875737851589</v>
-      </c>
-      <c r="V38">
-        <v>0.0016411661088852701</v>
-      </c>
-      <c r="W38">
-        <v>0.0022422053548026072</v>
-      </c>
-      <c r="X38">
-        <v>0.0011014995924897028</v>
-      </c>
-      <c r="Y38">
-        <v>-6.4030839606421357e-005</v>
-      </c>
-      <c r="Z38">
-        <v>-0.00065833618555343615</v>
-      </c>
-      <c r="AA38">
-        <v>0.0062824420735123664</v>
-      </c>
-      <c r="AB38">
-        <v>0.0010886179970883911</v>
-      </c>
-      <c r="AC38">
-        <v>0.0016366025266154058</v>
-      </c>
-      <c r="AD38">
-        <v>0.0028848712914047916</v>
-      </c>
-      <c r="AE38">
-        <v>0.0033297305422530492</v>
-      </c>
-      <c r="AF38">
-        <v>0.00015253190447202074</v>
-      </c>
-      <c r="AG38">
-        <v>-0.011262860929551824</v>
-      </c>
-      <c r="AH38">
-        <v>-0.016784359895925673</v>
-      </c>
-      <c r="AI38">
-        <v>0.0020466029037080891</v>
-      </c>
-      <c r="AJ38">
-        <v>0.00056406037807665149</v>
-      </c>
-      <c r="AK38">
-        <v>0.0020623072868582969</v>
-      </c>
-      <c r="AL38">
-        <v>0.018174698798309546</v>
-      </c>
-      <c r="AM38">
-        <v>0.85318039645179677</v>
+        <v>0.84587038546236482</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_fertility.xlsx
+++ b/input/reg_fertility.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="56">
   <si>
     <t>Description:</t>
   </si>
@@ -189,7 +189,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="13">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -248,6 +248,66 @@
       <name val="Calibri"/>
       <b/>
     </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -257,7 +317,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -307,11 +367,53 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -337,6 +439,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -350,7 +476,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -371,10 +497,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="9" t="s">
         <v>0</v>
       </c>
     </row>
@@ -387,7 +513,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
@@ -414,12 +540,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="12" t="s">
         <v>51</v>
       </c>
     </row>
